--- a/research/traditional_assets/database/data/canada/canada_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_electronics_consumer_office.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tsx_dbo" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0886</v>
+        <v>0.0251</v>
       </c>
       <c r="G2">
-        <v>-0.1391432308698496</v>
+        <v>-0.210529217199559</v>
       </c>
       <c r="H2">
-        <v>-0.2272073250490517</v>
+        <v>-0.3055953693495038</v>
       </c>
       <c r="I2">
-        <v>-0.2282210595160235</v>
+        <v>-0.318109151047409</v>
       </c>
       <c r="J2">
-        <v>-0.2282210595160235</v>
+        <v>-0.316642244553778</v>
       </c>
       <c r="K2">
-        <v>-9.475</v>
+        <v>-13.671</v>
       </c>
       <c r="L2">
-        <v>-0.3098430346631785</v>
+        <v>-0.376819184123484</v>
       </c>
       <c r="M2">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.3897507138998225</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-1.065963060686016</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +629,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>10.1</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>3.762</v>
+        <v>2.476</v>
       </c>
       <c r="V2">
-        <v>0.1451724936327854</v>
+        <v>0.100814332247557</v>
       </c>
       <c r="W2">
-        <v>-0.6366913195441268</v>
+        <v>-0.8349056603773585</v>
       </c>
       <c r="X2">
-        <v>0.123436936877717</v>
+        <v>0.09935269325950352</v>
       </c>
       <c r="Y2">
-        <v>-0.7601282564218439</v>
+        <v>-0.934258353636862</v>
       </c>
       <c r="Z2">
-        <v>2.419686659281532</v>
+        <v>3.195912614517266</v>
       </c>
       <c r="AA2">
-        <v>-0.2815836959153862</v>
+        <v>-0.8846918489065605</v>
       </c>
       <c r="AB2">
-        <v>0.1025708895507095</v>
+        <v>0.08637812484882795</v>
       </c>
       <c r="AC2">
-        <v>-0.383594222154561</v>
+        <v>-0.9737179153035521</v>
       </c>
       <c r="AD2">
-        <v>11.514</v>
+        <v>13.806</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.514</v>
+        <v>13.806</v>
       </c>
       <c r="AG2">
-        <v>7.752000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="AH2">
-        <v>0.3076306508496313</v>
+        <v>0.3598498670698014</v>
       </c>
       <c r="AI2">
-        <v>0.5064215341308937</v>
+        <v>1.070564516129032</v>
       </c>
       <c r="AJ2">
-        <v>0.2302619853858492</v>
+        <v>0.31568682084146</v>
       </c>
       <c r="AK2">
-        <v>0.4085590808474754</v>
+        <v>1.087332053742802</v>
       </c>
       <c r="AL2">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="AM2">
-        <v>1.529</v>
+        <v>2.407</v>
       </c>
       <c r="AN2">
-        <v>-2.279548604236785</v>
+        <v>-1.39313824419778</v>
       </c>
       <c r="AO2">
-        <v>-4.561437908496733</v>
+        <v>-4.788796680497924</v>
       </c>
       <c r="AP2">
-        <v>-1.534745594931697</v>
+        <v>-1.143289606458123</v>
       </c>
       <c r="AQ2">
-        <v>-4.564421190320471</v>
+        <v>-4.794765267968425</v>
       </c>
     </row>
     <row r="3">
@@ -719,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0492</v>
+        <v>0.0251</v>
       </c>
       <c r="G3">
-        <v>0.1569148936170213</v>
+        <v>0.1349358974358974</v>
       </c>
       <c r="H3">
-        <v>0.02978723404255319</v>
+        <v>0.03653846153846153</v>
       </c>
       <c r="I3">
-        <v>-0.01111702127659574</v>
+        <v>0.03009615384615385</v>
       </c>
       <c r="J3">
-        <v>-0.01111702127659574</v>
+        <v>0.02967980389176041</v>
       </c>
       <c r="K3">
-        <v>-0.594</v>
+        <v>0.499</v>
       </c>
       <c r="L3">
-        <v>-0.03159574468085106</v>
+        <v>0.01599358974358974</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,79 +754,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.87</v>
+        <v>2.13</v>
       </c>
       <c r="V3">
-        <v>0.2079710144927536</v>
+        <v>0.15</v>
       </c>
       <c r="W3">
-        <v>-0.06346153846153846</v>
+        <v>0.0619106699751861</v>
       </c>
       <c r="X3">
-        <v>0.1185727451031356</v>
+        <v>0.09935269325950352</v>
       </c>
       <c r="Y3">
-        <v>-0.182034283564674</v>
+        <v>-0.03744202328431742</v>
       </c>
       <c r="Z3">
-        <v>1.891348088531188</v>
+        <v>3.340471092077088</v>
       </c>
       <c r="AA3">
-        <v>-0.0210261569416499</v>
+        <v>0.09914452691894271</v>
       </c>
       <c r="AB3">
-        <v>0.1013548123912686</v>
+        <v>0.08637812484882795</v>
       </c>
       <c r="AC3">
-        <v>-0.1223809693329185</v>
+        <v>0.01276640207011476</v>
       </c>
       <c r="AD3">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.15</v>
+        <v>3.76</v>
       </c>
       <c r="AG3">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="AH3">
-        <v>0.2311977715877437</v>
+        <v>0.2093541202672606</v>
       </c>
       <c r="AI3">
-        <v>0.3398853398853399</v>
+        <v>0.2991249005568815</v>
       </c>
       <c r="AJ3">
-        <v>0.08488063660477455</v>
+        <v>0.1029690461149716</v>
       </c>
       <c r="AK3">
-        <v>0.1370449678800857</v>
+        <v>0.1561302681992337</v>
       </c>
       <c r="AL3">
-        <v>0.302</v>
+        <v>0.438</v>
       </c>
       <c r="AM3">
-        <v>0.301</v>
+        <v>0.435</v>
       </c>
       <c r="AN3">
-        <v>3.32</v>
+        <v>1.504</v>
       </c>
       <c r="AO3">
-        <v>-0.6920529801324503</v>
+        <v>2.143835616438356</v>
       </c>
       <c r="AP3">
-        <v>1.024</v>
+        <v>0.6519999999999999</v>
       </c>
       <c r="AQ3">
-        <v>-0.6943521594684385</v>
+        <v>2.158620689655173</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +837,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>International Parkside Products Inc. (TSXV:IPD)</t>
+          <t>Beacn Wizardry and Magic Inc. (TSXV:BECN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,26 +845,23 @@
           <t>Electronics (Consumer &amp; Office)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.128</v>
-      </c>
       <c r="G4">
-        <v>0.0007462686567164179</v>
+        <v>-0.06048780487804879</v>
       </c>
       <c r="H4">
-        <v>0.0007462686567164179</v>
+        <v>-0.1107317073170732</v>
       </c>
       <c r="I4">
-        <v>-0.03731343283582089</v>
+        <v>-0.8682926829268294</v>
       </c>
       <c r="J4">
-        <v>-0.03731343283582089</v>
+        <v>-0.8682926829268294</v>
       </c>
       <c r="K4">
-        <v>-0.101</v>
+        <v>-1.77</v>
       </c>
       <c r="L4">
-        <v>-0.03768656716417911</v>
+        <v>-0.8634146341463416</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,73 +885,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.111</v>
+        <v>0.319</v>
       </c>
       <c r="V4">
-        <v>0.2617924528301887</v>
+        <v>0.08885793871866296</v>
       </c>
       <c r="W4">
-        <v>-0.1532625189681335</v>
+        <v>-0.8349056603773585</v>
       </c>
       <c r="X4">
-        <v>0.1283011286522985</v>
+        <v>0.09193695228269919</v>
       </c>
       <c r="Y4">
-        <v>-0.281563647620432</v>
+        <v>-0.9268426126600576</v>
       </c>
       <c r="Z4">
-        <v>4.281150159744409</v>
+        <v>1.018886679920477</v>
       </c>
       <c r="AA4">
-        <v>-0.1597444089456869</v>
+        <v>-0.8846918489065605</v>
       </c>
       <c r="AB4">
-        <v>0.100234085768199</v>
+        <v>0.08902606639699166</v>
       </c>
       <c r="AC4">
-        <v>-0.2599784947138859</v>
+        <v>-0.9737179153035521</v>
       </c>
       <c r="AD4">
-        <v>0.212</v>
+        <v>0.236</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.212</v>
+        <v>0.236</v>
       </c>
       <c r="AG4">
-        <v>0.101</v>
+        <v>-0.08300000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.3333333333333333</v>
+        <v>0.06168322007318348</v>
       </c>
       <c r="AI4">
-        <v>0.2697201017811705</v>
+        <v>0.1018998272884283</v>
       </c>
       <c r="AJ4">
-        <v>0.1923809523809523</v>
+        <v>-0.02366695181066439</v>
       </c>
       <c r="AK4">
-        <v>0.1496296296296296</v>
+        <v>-0.04156234351527292</v>
       </c>
       <c r="AL4">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="AM4">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="AN4">
-        <v>-3.925925925925926</v>
+        <v>-0.1380116959064328</v>
       </c>
       <c r="AO4">
-        <v>-5.555555555555556</v>
+        <v>-890</v>
       </c>
       <c r="AP4">
-        <v>-1.87037037037037</v>
+        <v>0.04853801169590644</v>
       </c>
       <c r="AQ4">
-        <v>-5.555555555555556</v>
+        <v>-890</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +962,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beacn Wizardry and Magic Inc. (TSXV:BECN)</t>
+          <t>CE Brands Inc. (TSXV:CEBI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,22 +971,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-0.4280155642023347</v>
+        <v>-3.86930693069307</v>
       </c>
       <c r="H5">
-        <v>-0.4280155642023347</v>
+        <v>-3.960396039603961</v>
       </c>
       <c r="I5">
-        <v>-0.1284046692607004</v>
+        <v>-3.531353135313531</v>
       </c>
       <c r="J5">
-        <v>-0.1284046692607004</v>
+        <v>-3.531353135313531</v>
       </c>
       <c r="K5">
-        <v>-1.32</v>
+        <v>-12.4</v>
       </c>
       <c r="L5">
-        <v>-0.5136186770428016</v>
+        <v>-4.092409240924093</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,201 +1010,8836 @@
         <v>0</v>
       </c>
       <c r="U5">
+        <v>0.027</v>
+      </c>
+      <c r="V5">
+        <v>0.003988183161004431</v>
+      </c>
+      <c r="W5">
+        <v>-26.49572649572649</v>
+      </c>
+      <c r="X5">
+        <v>0.14347263593986</v>
+      </c>
+      <c r="Y5">
+        <v>-26.63919913166636</v>
+      </c>
+      <c r="AB5">
+        <v>0.08185986240728903</v>
+      </c>
+      <c r="AD5">
+        <v>9.81</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>9.81</v>
+      </c>
+      <c r="AG5">
+        <v>9.783000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.5916767189384802</v>
+      </c>
+      <c r="AI5">
+        <v>-4.92964824120603</v>
+      </c>
+      <c r="AJ5">
+        <v>0.5910106929257537</v>
+      </c>
+      <c r="AK5">
+        <v>-4.850272682201291</v>
+      </c>
+      <c r="AL5">
+        <v>1.97</v>
+      </c>
+      <c r="AM5">
+        <v>1.97</v>
+      </c>
+      <c r="AN5">
+        <v>-0.9168224299065422</v>
+      </c>
+      <c r="AO5">
+        <v>-5.431472081218274</v>
+      </c>
+      <c r="AP5">
+        <v>-0.9142990654205609</v>
+      </c>
+      <c r="AQ5">
+        <v>-5.431472081218274</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D-BOX Technologies Inc. (TSX:DBO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TSX:DBO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electronics (Consumer &amp; Office)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>3.28767123287671</v>
+      </c>
+      <c r="F2">
+        <v>4.51778893065139</v>
+      </c>
+      <c r="G2">
+        <v>1.504</v>
+      </c>
+      <c r="H2">
+        <v>3.592</v>
+      </c>
+      <c r="I2">
+        <v>0.209354120267261</v>
+      </c>
+      <c r="J2">
+        <v>0.5</v>
+      </c>
+      <c r="K2">
+        <v>14.2</v>
+      </c>
+      <c r="L2">
+        <v>9.7289703994216</v>
+      </c>
+      <c r="M2">
+        <v>15.83</v>
+      </c>
+      <c r="N2">
+        <v>16.5789703994216</v>
+      </c>
+      <c r="O2">
+        <v>3.76</v>
+      </c>
+      <c r="P2">
+        <v>8.98</v>
+      </c>
+      <c r="Q2">
+        <v>0.08637812484882799</v>
+      </c>
+      <c r="R2">
+        <v>0.08207745128493921</v>
+      </c>
+      <c r="S2">
+        <v>0.037378425</v>
+      </c>
+      <c r="T2">
+        <v>0.0374115</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.09935269325950349</v>
+      </c>
+      <c r="X2">
+        <v>0.126743402569878</v>
+      </c>
+      <c r="Y2">
+        <v>1.31636289694573</v>
+      </c>
+      <c r="Z2">
+        <v>1.91181309934518</v>
+      </c>
+      <c r="AA2">
+        <v>3.76</v>
+      </c>
+      <c r="AB2">
+        <v>0.050855</v>
+      </c>
+      <c r="AC2">
+        <v>3.287671232876712</v>
+      </c>
+      <c r="AD2">
+        <v>3.76</v>
+      </c>
+      <c r="AE2">
+        <v>0.438</v>
+      </c>
+      <c r="AF2">
+        <v>1.06</v>
+      </c>
+      <c r="AG2">
+        <v>2.5</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>14.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.265</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.5980000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>0.438</v>
+      </c>
+      <c r="AS2">
+        <v>3.76</v>
+      </c>
+      <c r="AT2">
+        <v>2.13</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08948784009791258</v>
+      </c>
+      <c r="C2">
+        <v>17.4592598356909</v>
+      </c>
+      <c r="D2">
+        <v>15.3292598356909</v>
+      </c>
+      <c r="E2">
+        <v>-3.76</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>2.13</v>
+      </c>
+      <c r="H2">
+        <v>14.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3.125</v>
+      </c>
+      <c r="K2">
+        <v>1.06</v>
+      </c>
+      <c r="L2">
+        <v>2.065</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2.065</v>
+      </c>
+      <c r="O2">
+        <v>0.547225</v>
+      </c>
+      <c r="P2">
+        <v>1.517775</v>
+      </c>
+      <c r="Q2">
+        <v>2.577775</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08948784009791258</v>
+      </c>
+      <c r="T2">
+        <v>1.101909567345926</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.265</v>
+      </c>
+      <c r="W2">
+        <v>0.0328545</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08929406232165311</v>
+      </c>
+      <c r="C3">
+        <v>17.3099354481664</v>
+      </c>
+      <c r="D3">
+        <v>15.3595354481664</v>
+      </c>
+      <c r="E3">
+        <v>-3.5804</v>
+      </c>
+      <c r="F3">
+        <v>0.1796</v>
+      </c>
+      <c r="G3">
+        <v>2.13</v>
+      </c>
+      <c r="H3">
+        <v>14.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>3.125</v>
+      </c>
+      <c r="K3">
+        <v>1.06</v>
+      </c>
+      <c r="L3">
+        <v>2.065</v>
+      </c>
+      <c r="M3">
+        <v>0.008028120000000001</v>
+      </c>
+      <c r="N3">
+        <v>2.05697188</v>
+      </c>
+      <c r="O3">
+        <v>0.5450975482</v>
+      </c>
+      <c r="P3">
+        <v>1.5118743318</v>
+      </c>
+      <c r="Q3">
+        <v>2.5718743318</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08986415891076072</v>
+      </c>
+      <c r="T3">
+        <v>1.110090411103494</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.265</v>
+      </c>
+      <c r="W3">
+        <v>0.0328545</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>257.2208686467068</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08910028454539365</v>
+      </c>
+      <c r="C4">
+        <v>17.16073088725227</v>
+      </c>
+      <c r="D4">
+        <v>15.38993088725227</v>
+      </c>
+      <c r="E4">
+        <v>-3.4008</v>
+      </c>
+      <c r="F4">
+        <v>0.3592</v>
+      </c>
+      <c r="G4">
+        <v>2.13</v>
+      </c>
+      <c r="H4">
+        <v>14.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3.125</v>
+      </c>
+      <c r="K4">
+        <v>1.06</v>
+      </c>
+      <c r="L4">
+        <v>2.065</v>
+      </c>
+      <c r="M4">
+        <v>0.01605624</v>
+      </c>
+      <c r="N4">
+        <v>2.04894376</v>
+      </c>
+      <c r="O4">
+        <v>0.5429700963999999</v>
+      </c>
+      <c r="P4">
+        <v>1.5059736636</v>
+      </c>
+      <c r="Q4">
+        <v>2.5659736636</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09024815769938127</v>
+      </c>
+      <c r="T4">
+        <v>1.118438210856114</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.265</v>
+      </c>
+      <c r="W4">
+        <v>0.0328545</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>128.6104343233534</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08890650676913417</v>
+      </c>
+      <c r="C5">
+        <v>17.01164686574435</v>
+      </c>
+      <c r="D5">
+        <v>15.42044686574435</v>
+      </c>
+      <c r="E5">
+        <v>-3.2212</v>
+      </c>
+      <c r="F5">
+        <v>0.5388000000000001</v>
+      </c>
+      <c r="G5">
+        <v>2.13</v>
+      </c>
+      <c r="H5">
+        <v>14.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3.125</v>
+      </c>
+      <c r="K5">
+        <v>1.06</v>
+      </c>
+      <c r="L5">
+        <v>2.065</v>
+      </c>
+      <c r="M5">
+        <v>0.02408436000000001</v>
+      </c>
+      <c r="N5">
+        <v>2.04091564</v>
+      </c>
+      <c r="O5">
+        <v>0.5408426446000001</v>
+      </c>
+      <c r="P5">
+        <v>1.5000729954</v>
+      </c>
+      <c r="Q5">
+        <v>2.5600729954</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09064007398879811</v>
+      </c>
+      <c r="T5">
+        <v>1.126958130191263</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.265</v>
+      </c>
+      <c r="W5">
+        <v>0.0328545</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>85.74028954890225</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08871272899287469</v>
+      </c>
+      <c r="C6">
+        <v>16.8626841021032</v>
+      </c>
+      <c r="D6">
+        <v>15.4510841021032</v>
+      </c>
+      <c r="E6">
+        <v>-3.0416</v>
+      </c>
+      <c r="F6">
+        <v>0.7184</v>
+      </c>
+      <c r="G6">
+        <v>2.13</v>
+      </c>
+      <c r="H6">
+        <v>14.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3.125</v>
+      </c>
+      <c r="K6">
+        <v>1.06</v>
+      </c>
+      <c r="L6">
+        <v>2.065</v>
+      </c>
+      <c r="M6">
+        <v>0.03211248000000001</v>
+      </c>
+      <c r="N6">
+        <v>2.03288752</v>
+      </c>
+      <c r="O6">
+        <v>0.5387151928</v>
+      </c>
+      <c r="P6">
+        <v>1.4941723272</v>
+      </c>
+      <c r="Q6">
+        <v>2.5541723272</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09104015520091115</v>
+      </c>
+      <c r="T6">
+        <v>1.135655547845895</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.265</v>
+      </c>
+      <c r="W6">
+        <v>0.0328545</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>64.30521716167669</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08851895121661522</v>
+      </c>
+      <c r="C7">
+        <v>16.71384332051047</v>
+      </c>
+      <c r="D7">
+        <v>15.48184332051047</v>
+      </c>
+      <c r="E7">
+        <v>-2.862</v>
+      </c>
+      <c r="F7">
+        <v>0.8980000000000001</v>
+      </c>
+      <c r="G7">
+        <v>2.13</v>
+      </c>
+      <c r="H7">
+        <v>14.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3.125</v>
+      </c>
+      <c r="K7">
+        <v>1.06</v>
+      </c>
+      <c r="L7">
+        <v>2.065</v>
+      </c>
+      <c r="M7">
+        <v>0.04014060000000001</v>
+      </c>
+      <c r="N7">
+        <v>2.0248594</v>
+      </c>
+      <c r="O7">
+        <v>0.5365877410000001</v>
+      </c>
+      <c r="P7">
+        <v>1.488271659</v>
+      </c>
+      <c r="Q7">
+        <v>2.548271659</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09144865917538446</v>
+      </c>
+      <c r="T7">
+        <v>1.144536069030097</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.265</v>
+      </c>
+      <c r="W7">
+        <v>0.0328545</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>51.44417372934135</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08832517344035576</v>
+      </c>
+      <c r="C8">
+        <v>16.56512525092597</v>
+      </c>
+      <c r="D8">
+        <v>15.51272525092597</v>
+      </c>
+      <c r="E8">
+        <v>-2.682399999999999</v>
+      </c>
+      <c r="F8">
+        <v>1.0776</v>
+      </c>
+      <c r="G8">
+        <v>2.13</v>
+      </c>
+      <c r="H8">
+        <v>14.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3.125</v>
+      </c>
+      <c r="K8">
+        <v>1.06</v>
+      </c>
+      <c r="L8">
+        <v>2.065</v>
+      </c>
+      <c r="M8">
+        <v>0.04816872000000001</v>
+      </c>
+      <c r="N8">
+        <v>2.01683128</v>
+      </c>
+      <c r="O8">
+        <v>0.5344602892</v>
+      </c>
+      <c r="P8">
+        <v>1.4823709908</v>
+      </c>
+      <c r="Q8">
+        <v>2.5423709908</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09186585472378272</v>
+      </c>
+      <c r="T8">
+        <v>1.153605537473537</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.265</v>
+      </c>
+      <c r="W8">
+        <v>0.0328545</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>42.87014477445113</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08813139566409631</v>
+      </c>
+      <c r="C9">
+        <v>16.41653062914542</v>
+      </c>
+      <c r="D9">
+        <v>15.54373062914542</v>
+      </c>
+      <c r="E9">
+        <v>-2.5028</v>
+      </c>
+      <c r="F9">
+        <v>1.2572</v>
+      </c>
+      <c r="G9">
+        <v>2.13</v>
+      </c>
+      <c r="H9">
+        <v>14.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3.125</v>
+      </c>
+      <c r="K9">
+        <v>1.06</v>
+      </c>
+      <c r="L9">
+        <v>2.065</v>
+      </c>
+      <c r="M9">
+        <v>0.05619684000000001</v>
+      </c>
+      <c r="N9">
+        <v>2.00880316</v>
+      </c>
+      <c r="O9">
+        <v>0.5323328373999999</v>
+      </c>
+      <c r="P9">
+        <v>1.4764703226</v>
+      </c>
+      <c r="Q9">
+        <v>2.5364703226</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.0922920222194584</v>
+      </c>
+      <c r="T9">
+        <v>1.162870048249095</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.265</v>
+      </c>
+      <c r="W9">
+        <v>0.0328545</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>36.74583837810096</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08793761788783684</v>
+      </c>
+      <c r="C10">
+        <v>16.26806019685885</v>
+      </c>
+      <c r="D10">
+        <v>15.57486019685885</v>
+      </c>
+      <c r="E10">
+        <v>-2.3232</v>
+      </c>
+      <c r="F10">
+        <v>1.4368</v>
+      </c>
+      <c r="G10">
+        <v>2.13</v>
+      </c>
+      <c r="H10">
+        <v>14.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3.125</v>
+      </c>
+      <c r="K10">
+        <v>1.06</v>
+      </c>
+      <c r="L10">
+        <v>2.065</v>
+      </c>
+      <c r="M10">
+        <v>0.06422496000000001</v>
+      </c>
+      <c r="N10">
+        <v>2.00077504</v>
+      </c>
+      <c r="O10">
+        <v>0.5302053856</v>
+      </c>
+      <c r="P10">
+        <v>1.4705696544</v>
+      </c>
+      <c r="Q10">
+        <v>2.5305696544</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09272745422590961</v>
+      </c>
+      <c r="T10">
+        <v>1.172335961432817</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.265</v>
+      </c>
+      <c r="W10">
+        <v>0.0328545</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>32.15260858083835</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08774384011157736</v>
+      </c>
+      <c r="C11">
+        <v>16.1197147017098</v>
+      </c>
+      <c r="D11">
+        <v>15.6061147017098</v>
+      </c>
+      <c r="E11">
+        <v>-2.1436</v>
+      </c>
+      <c r="F11">
+        <v>1.6164</v>
+      </c>
+      <c r="G11">
+        <v>2.13</v>
+      </c>
+      <c r="H11">
+        <v>14.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3.125</v>
+      </c>
+      <c r="K11">
+        <v>1.06</v>
+      </c>
+      <c r="L11">
+        <v>2.065</v>
+      </c>
+      <c r="M11">
+        <v>0.07225308000000001</v>
+      </c>
+      <c r="N11">
+        <v>1.99274692</v>
+      </c>
+      <c r="O11">
+        <v>0.5280779338</v>
+      </c>
+      <c r="P11">
+        <v>1.4646689862</v>
+      </c>
+      <c r="Q11">
+        <v>2.5246689862</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09317245616656852</v>
+      </c>
+      <c r="T11">
+        <v>1.182009916664533</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.265</v>
+      </c>
+      <c r="W11">
+        <v>0.0328545</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>28.58009651630075</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.0875500623353179</v>
+      </c>
+      <c r="C12">
+        <v>15.97149489735513</v>
+      </c>
+      <c r="D12">
+        <v>15.63749489735513</v>
+      </c>
+      <c r="E12">
+        <v>-1.964</v>
+      </c>
+      <c r="F12">
+        <v>1.796</v>
+      </c>
+      <c r="G12">
+        <v>2.13</v>
+      </c>
+      <c r="H12">
+        <v>14.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3.125</v>
+      </c>
+      <c r="K12">
+        <v>1.06</v>
+      </c>
+      <c r="L12">
+        <v>2.065</v>
+      </c>
+      <c r="M12">
+        <v>0.08028120000000002</v>
+      </c>
+      <c r="N12">
+        <v>1.9847188</v>
+      </c>
+      <c r="O12">
+        <v>0.5259504820000001</v>
+      </c>
+      <c r="P12">
+        <v>1.458768318</v>
+      </c>
+      <c r="Q12">
+        <v>2.518768318</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09362734703924211</v>
+      </c>
+      <c r="T12">
+        <v>1.191898848679176</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.265</v>
+      </c>
+      <c r="W12">
+        <v>0.0328545</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>25.72208686467068</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08735628455905843</v>
+      </c>
+      <c r="C13">
+        <v>15.82340154352561</v>
+      </c>
+      <c r="D13">
+        <v>15.66900154352561</v>
+      </c>
+      <c r="E13">
+        <v>-1.7844</v>
+      </c>
+      <c r="F13">
+        <v>1.9756</v>
+      </c>
+      <c r="G13">
+        <v>2.13</v>
+      </c>
+      <c r="H13">
+        <v>14.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3.125</v>
+      </c>
+      <c r="K13">
+        <v>1.06</v>
+      </c>
+      <c r="L13">
+        <v>2.065</v>
+      </c>
+      <c r="M13">
+        <v>0.08830932000000001</v>
+      </c>
+      <c r="N13">
+        <v>1.97669068</v>
+      </c>
+      <c r="O13">
+        <v>0.5238230302</v>
+      </c>
+      <c r="P13">
+        <v>1.4528676498</v>
+      </c>
+      <c r="Q13">
+        <v>2.5128676498</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09409246017871734</v>
+      </c>
+      <c r="T13">
+        <v>1.202010003885159</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.265</v>
+      </c>
+      <c r="W13">
+        <v>0.0328545</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>23.3837153315188</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08716250678279895</v>
+      </c>
+      <c r="C14">
+        <v>15.67543540608726</v>
+      </c>
+      <c r="D14">
+        <v>15.70063540608726</v>
+      </c>
+      <c r="E14">
+        <v>-1.6048</v>
+      </c>
+      <c r="F14">
+        <v>2.1552</v>
+      </c>
+      <c r="G14">
+        <v>2.13</v>
+      </c>
+      <c r="H14">
+        <v>14.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3.125</v>
+      </c>
+      <c r="K14">
+        <v>1.06</v>
+      </c>
+      <c r="L14">
+        <v>2.065</v>
+      </c>
+      <c r="M14">
+        <v>0.09633744000000002</v>
+      </c>
+      <c r="N14">
+        <v>1.96866256</v>
+      </c>
+      <c r="O14">
+        <v>0.5216955784</v>
+      </c>
+      <c r="P14">
+        <v>1.4469669816</v>
+      </c>
+      <c r="Q14">
+        <v>2.5069669816</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09456814407136245</v>
+      </c>
+      <c r="T14">
+        <v>1.212350958073097</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.265</v>
+      </c>
+      <c r="W14">
+        <v>0.0328545</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>21.43507238722556</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08696872900653949</v>
+      </c>
+      <c r="C15">
+        <v>15.52759725710336</v>
+      </c>
+      <c r="D15">
+        <v>15.73239725710336</v>
+      </c>
+      <c r="E15">
+        <v>-1.4252</v>
+      </c>
+      <c r="F15">
+        <v>2.3348</v>
+      </c>
+      <c r="G15">
+        <v>2.13</v>
+      </c>
+      <c r="H15">
+        <v>14.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3.125</v>
+      </c>
+      <c r="K15">
+        <v>1.06</v>
+      </c>
+      <c r="L15">
+        <v>2.065</v>
+      </c>
+      <c r="M15">
+        <v>0.10436556</v>
+      </c>
+      <c r="N15">
+        <v>1.96063444</v>
+      </c>
+      <c r="O15">
+        <v>0.5195681266000001</v>
+      </c>
+      <c r="P15">
+        <v>1.4410663134</v>
+      </c>
+      <c r="Q15">
+        <v>2.5010663134</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09505476322590746</v>
+      </c>
+      <c r="T15">
+        <v>1.222929635345814</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.265</v>
+      </c>
+      <c r="W15">
+        <v>0.0328545</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>19.78622066513129</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08677495123028001</v>
+      </c>
+      <c r="C16">
+        <v>15.37988787489728</v>
+      </c>
+      <c r="D16">
+        <v>15.76428787489728</v>
+      </c>
+      <c r="E16">
+        <v>-1.2456</v>
+      </c>
+      <c r="F16">
+        <v>2.5144</v>
+      </c>
+      <c r="G16">
+        <v>2.13</v>
+      </c>
+      <c r="H16">
+        <v>14.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3.125</v>
+      </c>
+      <c r="K16">
+        <v>1.06</v>
+      </c>
+      <c r="L16">
+        <v>2.065</v>
+      </c>
+      <c r="M16">
+        <v>0.11239368</v>
+      </c>
+      <c r="N16">
+        <v>1.95260632</v>
+      </c>
+      <c r="O16">
+        <v>0.5174406748</v>
+      </c>
+      <c r="P16">
+        <v>1.4351656452</v>
+      </c>
+      <c r="Q16">
+        <v>2.4951656452</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09555269910497677</v>
+      </c>
+      <c r="T16">
+        <v>1.23375432836906</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.265</v>
+      </c>
+      <c r="W16">
+        <v>0.0328545</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>18.37291918905048</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08658117345402055</v>
+      </c>
+      <c r="C17">
+        <v>15.2323080441161</v>
+      </c>
+      <c r="D17">
+        <v>15.7963080441161</v>
+      </c>
+      <c r="E17">
+        <v>-1.066</v>
+      </c>
+      <c r="F17">
+        <v>2.694</v>
+      </c>
+      <c r="G17">
+        <v>2.13</v>
+      </c>
+      <c r="H17">
+        <v>14.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3.125</v>
+      </c>
+      <c r="K17">
+        <v>1.06</v>
+      </c>
+      <c r="L17">
+        <v>2.065</v>
+      </c>
+      <c r="M17">
+        <v>0.1204218</v>
+      </c>
+      <c r="N17">
+        <v>1.9445782</v>
+      </c>
+      <c r="O17">
+        <v>0.515313223</v>
+      </c>
+      <c r="P17">
+        <v>1.429264977</v>
+      </c>
+      <c r="Q17">
+        <v>2.489264977</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09606235112237711</v>
+      </c>
+      <c r="T17">
+        <v>1.244833720051676</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.265</v>
+      </c>
+      <c r="W17">
+        <v>0.0328545</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>17.14805790978046</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08638739567776109</v>
+      </c>
+      <c r="C18">
+        <v>15.08485855579487</v>
+      </c>
+      <c r="D18">
+        <v>15.82845855579487</v>
+      </c>
+      <c r="E18">
+        <v>-0.8863999999999996</v>
+      </c>
+      <c r="F18">
+        <v>2.8736</v>
+      </c>
+      <c r="G18">
+        <v>2.13</v>
+      </c>
+      <c r="H18">
+        <v>14.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3.125</v>
+      </c>
+      <c r="K18">
+        <v>1.06</v>
+      </c>
+      <c r="L18">
+        <v>2.065</v>
+      </c>
+      <c r="M18">
+        <v>0.12844992</v>
+      </c>
+      <c r="N18">
+        <v>1.93655008</v>
+      </c>
+      <c r="O18">
+        <v>0.5131857712</v>
+      </c>
+      <c r="P18">
+        <v>1.4233643088</v>
+      </c>
+      <c r="Q18">
+        <v>2.4833643088</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09658413771162035</v>
+      </c>
+      <c r="T18">
+        <v>1.256176906774355</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.265</v>
+      </c>
+      <c r="W18">
+        <v>0.0328545</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>16.07630429041917</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08619361790150161</v>
+      </c>
+      <c r="C19">
+        <v>14.93754020742187</v>
+      </c>
+      <c r="D19">
+        <v>15.86074020742187</v>
+      </c>
+      <c r="E19">
+        <v>-0.7067999999999994</v>
+      </c>
+      <c r="F19">
+        <v>3.0532</v>
+      </c>
+      <c r="G19">
+        <v>2.13</v>
+      </c>
+      <c r="H19">
+        <v>14.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3.125</v>
+      </c>
+      <c r="K19">
+        <v>1.06</v>
+      </c>
+      <c r="L19">
+        <v>2.065</v>
+      </c>
+      <c r="M19">
+        <v>0.13647804</v>
+      </c>
+      <c r="N19">
+        <v>1.92852196</v>
+      </c>
+      <c r="O19">
+        <v>0.5110583194</v>
+      </c>
+      <c r="P19">
+        <v>1.4174636406</v>
+      </c>
+      <c r="Q19">
+        <v>2.4774636406</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09711849747168869</v>
+      </c>
+      <c r="T19">
+        <v>1.26779342329758</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.265</v>
+      </c>
+      <c r="W19">
+        <v>0.0328545</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>15.13063933215922</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08599984012524216</v>
+      </c>
+      <c r="C20">
+        <v>14.79035380300442</v>
+      </c>
+      <c r="D20">
+        <v>15.89315380300442</v>
+      </c>
+      <c r="E20">
+        <v>-0.5271999999999997</v>
+      </c>
+      <c r="F20">
+        <v>3.2328</v>
+      </c>
+      <c r="G20">
+        <v>2.13</v>
+      </c>
+      <c r="H20">
+        <v>14.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3.125</v>
+      </c>
+      <c r="K20">
+        <v>1.06</v>
+      </c>
+      <c r="L20">
+        <v>2.065</v>
+      </c>
+      <c r="M20">
+        <v>0.14450616</v>
+      </c>
+      <c r="N20">
+        <v>1.92049384</v>
+      </c>
+      <c r="O20">
+        <v>0.5089308676000001</v>
+      </c>
+      <c r="P20">
+        <v>1.4115629724</v>
+      </c>
+      <c r="Q20">
+        <v>2.4715629724</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09766589039663677</v>
+      </c>
+      <c r="T20">
+        <v>1.279693269492104</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.265</v>
+      </c>
+      <c r="W20">
+        <v>0.0328545</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>14.29004825815038</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08580606234898269</v>
+      </c>
+      <c r="C21">
+        <v>14.64330015313575</v>
+      </c>
+      <c r="D21">
+        <v>15.92570015313575</v>
+      </c>
+      <c r="E21">
+        <v>-0.3475999999999995</v>
+      </c>
+      <c r="F21">
+        <v>3.4124</v>
+      </c>
+      <c r="G21">
+        <v>2.13</v>
+      </c>
+      <c r="H21">
+        <v>14.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3.125</v>
+      </c>
+      <c r="K21">
+        <v>1.06</v>
+      </c>
+      <c r="L21">
+        <v>2.065</v>
+      </c>
+      <c r="M21">
+        <v>0.15253428</v>
+      </c>
+      <c r="N21">
+        <v>1.91246572</v>
+      </c>
+      <c r="O21">
+        <v>0.5068034158</v>
+      </c>
+      <c r="P21">
+        <v>1.4056623042</v>
+      </c>
+      <c r="Q21">
+        <v>2.4656623042</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09822679919627492</v>
+      </c>
+      <c r="T21">
+        <v>1.291886939049455</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.265</v>
+      </c>
+      <c r="W21">
+        <v>0.0328545</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>13.53794045508983</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08561228457272321</v>
+      </c>
+      <c r="C22">
+        <v>14.49638007506249</v>
+      </c>
+      <c r="D22">
+        <v>15.95838007506249</v>
+      </c>
+      <c r="E22">
+        <v>-0.1679999999999993</v>
+      </c>
+      <c r="F22">
+        <v>3.592000000000001</v>
+      </c>
+      <c r="G22">
+        <v>2.13</v>
+      </c>
+      <c r="H22">
+        <v>14.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3.125</v>
+      </c>
+      <c r="K22">
+        <v>1.06</v>
+      </c>
+      <c r="L22">
+        <v>2.065</v>
+      </c>
+      <c r="M22">
+        <v>0.1605624</v>
+      </c>
+      <c r="N22">
+        <v>1.9044376</v>
+      </c>
+      <c r="O22">
+        <v>0.504675964</v>
+      </c>
+      <c r="P22">
+        <v>1.399761636</v>
+      </c>
+      <c r="Q22">
+        <v>2.459761636</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09880173071590401</v>
+      </c>
+      <c r="T22">
+        <v>1.304385450345739</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.265</v>
+      </c>
+      <c r="W22">
+        <v>0.0328545</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>12.86104343233534</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08558829179646375</v>
+      </c>
+      <c r="C23">
+        <v>14.3208357036248</v>
+      </c>
+      <c r="D23">
+        <v>15.9624357036248</v>
+      </c>
+      <c r="E23">
+        <v>0.01160000000000005</v>
+      </c>
+      <c r="F23">
+        <v>3.7716</v>
+      </c>
+      <c r="G23">
+        <v>2.13</v>
+      </c>
+      <c r="H23">
+        <v>14.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3.125</v>
+      </c>
+      <c r="K23">
+        <v>1.06</v>
+      </c>
+      <c r="L23">
+        <v>2.065</v>
+      </c>
+      <c r="M23">
+        <v>0.17273928</v>
+      </c>
+      <c r="N23">
+        <v>1.89226072</v>
+      </c>
+      <c r="O23">
+        <v>0.5014490908</v>
+      </c>
+      <c r="P23">
+        <v>1.3908116292</v>
+      </c>
+      <c r="Q23">
+        <v>2.4508116292</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09939121746387816</v>
+      </c>
+      <c r="T23">
+        <v>1.317200379649525</v>
+      </c>
+      <c r="U23">
+        <v>0.0458</v>
+      </c>
+      <c r="V23">
+        <v>0.265</v>
+      </c>
+      <c r="W23">
+        <v>0.033663</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>11.95443213610709</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08540259902020428</v>
+      </c>
+      <c r="C24">
+        <v>14.17269420957803</v>
+      </c>
+      <c r="D24">
+        <v>15.99389420957803</v>
+      </c>
+      <c r="E24">
+        <v>0.1912000000000003</v>
+      </c>
+      <c r="F24">
+        <v>3.9512</v>
+      </c>
+      <c r="G24">
+        <v>2.13</v>
+      </c>
+      <c r="H24">
+        <v>14.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3.125</v>
+      </c>
+      <c r="K24">
+        <v>1.06</v>
+      </c>
+      <c r="L24">
+        <v>2.065</v>
+      </c>
+      <c r="M24">
+        <v>0.18096496</v>
+      </c>
+      <c r="N24">
+        <v>1.88403504</v>
+      </c>
+      <c r="O24">
+        <v>0.4992692856</v>
+      </c>
+      <c r="P24">
+        <v>1.3847657544</v>
+      </c>
+      <c r="Q24">
+        <v>2.4447657544</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09999581925667214</v>
+      </c>
+      <c r="T24">
+        <v>1.330343896884177</v>
+      </c>
+      <c r="U24">
+        <v>0.0458</v>
+      </c>
+      <c r="V24">
+        <v>0.265</v>
+      </c>
+      <c r="W24">
+        <v>0.033663</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>11.41104885719313</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08521690624394482</v>
+      </c>
+      <c r="C25">
+        <v>14.02467695619578</v>
+      </c>
+      <c r="D25">
+        <v>16.02547695619579</v>
+      </c>
+      <c r="E25">
+        <v>0.3708000000000009</v>
+      </c>
+      <c r="F25">
+        <v>4.130800000000001</v>
+      </c>
+      <c r="G25">
+        <v>2.13</v>
+      </c>
+      <c r="H25">
+        <v>14.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3.125</v>
+      </c>
+      <c r="K25">
+        <v>1.06</v>
+      </c>
+      <c r="L25">
+        <v>2.065</v>
+      </c>
+      <c r="M25">
+        <v>0.18919064</v>
+      </c>
+      <c r="N25">
+        <v>1.87580936</v>
+      </c>
+      <c r="O25">
+        <v>0.4970894804</v>
+      </c>
+      <c r="P25">
+        <v>1.3787198796</v>
+      </c>
+      <c r="Q25">
+        <v>2.4387198796</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1006161249921361</v>
+      </c>
+      <c r="T25">
+        <v>1.343828804176872</v>
+      </c>
+      <c r="U25">
+        <v>0.0458</v>
+      </c>
+      <c r="V25">
+        <v>0.265</v>
+      </c>
+      <c r="W25">
+        <v>0.033663</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>10.91491629818473</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08503121346768533</v>
+      </c>
+      <c r="C26">
+        <v>13.8767846809392</v>
+      </c>
+      <c r="D26">
+        <v>16.0571846809392</v>
+      </c>
+      <c r="E26">
+        <v>0.5504000000000007</v>
+      </c>
+      <c r="F26">
+        <v>4.3104</v>
+      </c>
+      <c r="G26">
+        <v>2.13</v>
+      </c>
+      <c r="H26">
+        <v>14.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3.125</v>
+      </c>
+      <c r="K26">
+        <v>1.06</v>
+      </c>
+      <c r="L26">
+        <v>2.065</v>
+      </c>
+      <c r="M26">
+        <v>0.19741632</v>
+      </c>
+      <c r="N26">
+        <v>1.86758368</v>
+      </c>
+      <c r="O26">
+        <v>0.4949096752</v>
+      </c>
+      <c r="P26">
+        <v>1.3726740048</v>
+      </c>
+      <c r="Q26">
+        <v>2.4326740048</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1012527545627439</v>
+      </c>
+      <c r="T26">
+        <v>1.357668577450954</v>
+      </c>
+      <c r="U26">
+        <v>0.0458</v>
+      </c>
+      <c r="V26">
+        <v>0.265</v>
+      </c>
+      <c r="W26">
+        <v>0.033663</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>10.4601281190937</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08484552069142587</v>
+      </c>
+      <c r="C27">
+        <v>13.72901812711749</v>
+      </c>
+      <c r="D27">
+        <v>16.08901812711749</v>
+      </c>
+      <c r="E27">
+        <v>0.7300000000000004</v>
+      </c>
+      <c r="F27">
+        <v>4.49</v>
+      </c>
+      <c r="G27">
+        <v>2.13</v>
+      </c>
+      <c r="H27">
+        <v>14.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3.125</v>
+      </c>
+      <c r="K27">
+        <v>1.06</v>
+      </c>
+      <c r="L27">
+        <v>2.065</v>
+      </c>
+      <c r="M27">
+        <v>0.205642</v>
+      </c>
+      <c r="N27">
+        <v>1.859358</v>
+      </c>
+      <c r="O27">
+        <v>0.49272987</v>
+      </c>
+      <c r="P27">
+        <v>1.36662813</v>
+      </c>
+      <c r="Q27">
+        <v>2.42662813</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1019063609219012</v>
+      </c>
+      <c r="T27">
+        <v>1.371877411345678</v>
+      </c>
+      <c r="U27">
+        <v>0.0458</v>
+      </c>
+      <c r="V27">
+        <v>0.265</v>
+      </c>
+      <c r="W27">
+        <v>0.033663</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>10.04172299432995</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.0850802479151664</v>
+      </c>
+      <c r="C28">
+        <v>13.50919968322718</v>
+      </c>
+      <c r="D28">
+        <v>16.04879968322718</v>
+      </c>
+      <c r="E28">
+        <v>0.9096000000000002</v>
+      </c>
+      <c r="F28">
+        <v>4.6696</v>
+      </c>
+      <c r="G28">
+        <v>2.13</v>
+      </c>
+      <c r="H28">
+        <v>14.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3.125</v>
+      </c>
+      <c r="K28">
+        <v>1.06</v>
+      </c>
+      <c r="L28">
+        <v>2.065</v>
+      </c>
+      <c r="M28">
+        <v>0.2241408</v>
+      </c>
+      <c r="N28">
+        <v>1.8408592</v>
+      </c>
+      <c r="O28">
+        <v>0.487827688</v>
+      </c>
+      <c r="P28">
+        <v>1.353031512</v>
+      </c>
+      <c r="Q28">
+        <v>2.413031512</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1025776323177924</v>
+      </c>
+      <c r="T28">
+        <v>1.386470267778096</v>
+      </c>
+      <c r="U28">
+        <v>0.048</v>
+      </c>
+      <c r="V28">
+        <v>0.265</v>
+      </c>
+      <c r="W28">
+        <v>0.03528</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>9.212958997201758</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.08491072513890692</v>
+      </c>
+      <c r="C29">
+        <v>13.35862571274917</v>
+      </c>
+      <c r="D29">
+        <v>16.07782571274917</v>
+      </c>
+      <c r="E29">
+        <v>1.089200000000001</v>
+      </c>
+      <c r="F29">
+        <v>4.849200000000001</v>
+      </c>
+      <c r="G29">
+        <v>2.13</v>
+      </c>
+      <c r="H29">
+        <v>14.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3.125</v>
+      </c>
+      <c r="K29">
+        <v>1.06</v>
+      </c>
+      <c r="L29">
+        <v>2.065</v>
+      </c>
+      <c r="M29">
+        <v>0.2327616</v>
+      </c>
+      <c r="N29">
+        <v>1.8322384</v>
+      </c>
+      <c r="O29">
+        <v>0.485543176</v>
+      </c>
+      <c r="P29">
+        <v>1.346695224</v>
+      </c>
+      <c r="Q29">
+        <v>2.406695224</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1032672947108314</v>
+      </c>
+      <c r="T29">
+        <v>1.401462928496335</v>
+      </c>
+      <c r="U29">
+        <v>0.048</v>
+      </c>
+      <c r="V29">
+        <v>0.265</v>
+      </c>
+      <c r="W29">
+        <v>0.03528</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>8.871738293601691</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.08474120236264747</v>
+      </c>
+      <c r="C30">
+        <v>13.20815692607813</v>
+      </c>
+      <c r="D30">
+        <v>16.10695692607813</v>
+      </c>
+      <c r="E30">
+        <v>1.268800000000001</v>
+      </c>
+      <c r="F30">
+        <v>5.0288</v>
+      </c>
+      <c r="G30">
+        <v>2.13</v>
+      </c>
+      <c r="H30">
+        <v>14.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3.125</v>
+      </c>
+      <c r="K30">
+        <v>1.06</v>
+      </c>
+      <c r="L30">
+        <v>2.065</v>
+      </c>
+      <c r="M30">
+        <v>0.2413824</v>
+      </c>
+      <c r="N30">
+        <v>1.8236176</v>
+      </c>
+      <c r="O30">
+        <v>0.483258664</v>
+      </c>
+      <c r="P30">
+        <v>1.340358936</v>
+      </c>
+      <c r="Q30">
+        <v>2.400358936</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1039761143925659</v>
+      </c>
+      <c r="T30">
+        <v>1.416872052012303</v>
+      </c>
+      <c r="U30">
+        <v>0.048</v>
+      </c>
+      <c r="V30">
+        <v>0.265</v>
+      </c>
+      <c r="W30">
+        <v>0.03528</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>8.554890497401633</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.08457167958638799</v>
+      </c>
+      <c r="C31">
+        <v>13.05779389599558</v>
+      </c>
+      <c r="D31">
+        <v>16.13619389599558</v>
+      </c>
+      <c r="E31">
+        <v>1.4484</v>
+      </c>
+      <c r="F31">
+        <v>5.2084</v>
+      </c>
+      <c r="G31">
+        <v>2.13</v>
+      </c>
+      <c r="H31">
+        <v>14.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3.125</v>
+      </c>
+      <c r="K31">
+        <v>1.06</v>
+      </c>
+      <c r="L31">
+        <v>2.065</v>
+      </c>
+      <c r="M31">
+        <v>0.2500032</v>
+      </c>
+      <c r="N31">
+        <v>1.8149968</v>
+      </c>
+      <c r="O31">
+        <v>0.480974152</v>
+      </c>
+      <c r="P31">
+        <v>1.334022648</v>
+      </c>
+      <c r="Q31">
+        <v>2.394022648</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1047049008258986</v>
+      </c>
+      <c r="T31">
+        <v>1.432715235345622</v>
+      </c>
+      <c r="U31">
+        <v>0.048</v>
+      </c>
+      <c r="V31">
+        <v>0.265</v>
+      </c>
+      <c r="W31">
+        <v>0.03528</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>8.2598942733533</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08440215681012853</v>
+      </c>
+      <c r="C32">
+        <v>12.90753719944941</v>
+      </c>
+      <c r="D32">
+        <v>16.16553719944941</v>
+      </c>
+      <c r="E32">
+        <v>1.628</v>
+      </c>
+      <c r="F32">
+        <v>5.388</v>
+      </c>
+      <c r="G32">
+        <v>2.13</v>
+      </c>
+      <c r="H32">
+        <v>14.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3.125</v>
+      </c>
+      <c r="K32">
+        <v>1.06</v>
+      </c>
+      <c r="L32">
+        <v>2.065</v>
+      </c>
+      <c r="M32">
+        <v>0.258624</v>
+      </c>
+      <c r="N32">
+        <v>1.806376</v>
+      </c>
+      <c r="O32">
+        <v>0.47868964</v>
+      </c>
+      <c r="P32">
+        <v>1.32768636</v>
+      </c>
+      <c r="Q32">
+        <v>2.38768636</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.105454509728755</v>
+      </c>
+      <c r="T32">
+        <v>1.449011081059892</v>
+      </c>
+      <c r="U32">
+        <v>0.048</v>
+      </c>
+      <c r="V32">
+        <v>0.265</v>
+      </c>
+      <c r="W32">
+        <v>0.03528</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>7.984564464241524</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.08457440903386905</v>
+      </c>
+      <c r="C33">
+        <v>12.69812231753428</v>
+      </c>
+      <c r="D33">
+        <v>16.13572231753428</v>
+      </c>
+      <c r="E33">
+        <v>1.807600000000001</v>
+      </c>
+      <c r="F33">
+        <v>5.567600000000001</v>
+      </c>
+      <c r="G33">
+        <v>2.13</v>
+      </c>
+      <c r="H33">
+        <v>14.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3.125</v>
+      </c>
+      <c r="K33">
+        <v>1.06</v>
+      </c>
+      <c r="L33">
+        <v>2.065</v>
+      </c>
+      <c r="M33">
+        <v>0.2755962</v>
+      </c>
+      <c r="N33">
+        <v>1.7894038</v>
+      </c>
+      <c r="O33">
+        <v>0.474192007</v>
+      </c>
+      <c r="P33">
+        <v>1.315211793</v>
+      </c>
+      <c r="Q33">
+        <v>2.375211793</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1062258464258972</v>
+      </c>
+      <c r="T33">
+        <v>1.4657792701282</v>
+      </c>
+      <c r="U33">
+        <v>0.0495</v>
+      </c>
+      <c r="V33">
+        <v>0.265</v>
+      </c>
+      <c r="W33">
+        <v>0.0363825</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>7.492846418056562</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08441591125760958</v>
+      </c>
+      <c r="C34">
+        <v>12.54595241537633</v>
+      </c>
+      <c r="D34">
+        <v>16.16315241537633</v>
+      </c>
+      <c r="E34">
+        <v>1.987200000000001</v>
+      </c>
+      <c r="F34">
+        <v>5.7472</v>
+      </c>
+      <c r="G34">
+        <v>2.13</v>
+      </c>
+      <c r="H34">
+        <v>14.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3.125</v>
+      </c>
+      <c r="K34">
+        <v>1.06</v>
+      </c>
+      <c r="L34">
+        <v>2.065</v>
+      </c>
+      <c r="M34">
+        <v>0.2844864</v>
+      </c>
+      <c r="N34">
+        <v>1.7805136</v>
+      </c>
+      <c r="O34">
+        <v>0.471836104</v>
+      </c>
+      <c r="P34">
+        <v>1.308677496</v>
+      </c>
+      <c r="Q34">
+        <v>2.368677496</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1070198694964847</v>
+      </c>
+      <c r="T34">
+        <v>1.483040641227928</v>
+      </c>
+      <c r="U34">
+        <v>0.0495</v>
+      </c>
+      <c r="V34">
+        <v>0.265</v>
+      </c>
+      <c r="W34">
+        <v>0.0363825</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>7.258694967492294</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.08425741348135012</v>
+      </c>
+      <c r="C35">
+        <v>12.39387593221742</v>
+      </c>
+      <c r="D35">
+        <v>16.19067593221742</v>
+      </c>
+      <c r="E35">
+        <v>2.166800000000001</v>
+      </c>
+      <c r="F35">
+        <v>5.926800000000001</v>
+      </c>
+      <c r="G35">
+        <v>2.13</v>
+      </c>
+      <c r="H35">
+        <v>14.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3.125</v>
+      </c>
+      <c r="K35">
+        <v>1.06</v>
+      </c>
+      <c r="L35">
+        <v>2.065</v>
+      </c>
+      <c r="M35">
+        <v>0.2933766</v>
+      </c>
+      <c r="N35">
+        <v>1.7716234</v>
+      </c>
+      <c r="O35">
+        <v>0.469480201</v>
+      </c>
+      <c r="P35">
+        <v>1.302143199</v>
+      </c>
+      <c r="Q35">
+        <v>2.362143199</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1078375947482838</v>
+      </c>
+      <c r="T35">
+        <v>1.500817277136604</v>
+      </c>
+      <c r="U35">
+        <v>0.0495</v>
+      </c>
+      <c r="V35">
+        <v>0.265</v>
+      </c>
+      <c r="W35">
+        <v>0.0363825</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.038734513931922</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08409891570509065</v>
+      </c>
+      <c r="C36">
+        <v>12.24189334610882</v>
+      </c>
+      <c r="D36">
+        <v>16.21829334610882</v>
+      </c>
+      <c r="E36">
+        <v>2.346400000000001</v>
+      </c>
+      <c r="F36">
+        <v>6.106400000000001</v>
+      </c>
+      <c r="G36">
+        <v>2.13</v>
+      </c>
+      <c r="H36">
+        <v>14.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3.125</v>
+      </c>
+      <c r="K36">
+        <v>1.06</v>
+      </c>
+      <c r="L36">
+        <v>2.065</v>
+      </c>
+      <c r="M36">
+        <v>0.3022668000000001</v>
+      </c>
+      <c r="N36">
+        <v>1.7627332</v>
+      </c>
+      <c r="O36">
+        <v>0.467124298</v>
+      </c>
+      <c r="P36">
+        <v>1.295608902</v>
+      </c>
+      <c r="Q36">
+        <v>2.355608902</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1086800995531677</v>
+      </c>
+      <c r="T36">
+        <v>1.519132598981906</v>
+      </c>
+      <c r="U36">
+        <v>0.0495</v>
+      </c>
+      <c r="V36">
+        <v>0.265</v>
+      </c>
+      <c r="W36">
+        <v>0.0363825</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>6.831712910580983</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08394041792883118</v>
+      </c>
+      <c r="C37">
+        <v>12.09000513836916</v>
+      </c>
+      <c r="D37">
+        <v>16.24600513836917</v>
+      </c>
+      <c r="E37">
+        <v>2.526000000000001</v>
+      </c>
+      <c r="F37">
+        <v>6.286</v>
+      </c>
+      <c r="G37">
+        <v>2.13</v>
+      </c>
+      <c r="H37">
+        <v>14.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3.125</v>
+      </c>
+      <c r="K37">
+        <v>1.06</v>
+      </c>
+      <c r="L37">
+        <v>2.065</v>
+      </c>
+      <c r="M37">
+        <v>0.311157</v>
+      </c>
+      <c r="N37">
+        <v>1.753843</v>
+      </c>
+      <c r="O37">
+        <v>0.464768395</v>
+      </c>
+      <c r="P37">
+        <v>1.289074605</v>
+      </c>
+      <c r="Q37">
+        <v>2.349074605</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1095485275828172</v>
+      </c>
+      <c r="T37">
+        <v>1.538011469191679</v>
+      </c>
+      <c r="U37">
+        <v>0.0495</v>
+      </c>
+      <c r="V37">
+        <v>0.265</v>
+      </c>
+      <c r="W37">
+        <v>0.0363825</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>6.636521113135812</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08378192015257171</v>
+      </c>
+      <c r="C38">
+        <v>11.93821179361238</v>
+      </c>
+      <c r="D38">
+        <v>16.27381179361238</v>
+      </c>
+      <c r="E38">
+        <v>2.7056</v>
+      </c>
+      <c r="F38">
+        <v>6.4656</v>
+      </c>
+      <c r="G38">
+        <v>2.13</v>
+      </c>
+      <c r="H38">
+        <v>14.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3.125</v>
+      </c>
+      <c r="K38">
+        <v>1.06</v>
+      </c>
+      <c r="L38">
+        <v>2.065</v>
+      </c>
+      <c r="M38">
+        <v>0.3200472</v>
+      </c>
+      <c r="N38">
+        <v>1.7449528</v>
+      </c>
+      <c r="O38">
+        <v>0.462412492</v>
+      </c>
+      <c r="P38">
+        <v>1.282540308</v>
+      </c>
+      <c r="Q38">
+        <v>2.342540308</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1104440939883933</v>
+      </c>
+      <c r="T38">
+        <v>1.557480304095507</v>
+      </c>
+      <c r="U38">
+        <v>0.0495</v>
+      </c>
+      <c r="V38">
+        <v>0.265</v>
+      </c>
+      <c r="W38">
+        <v>0.0363825</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.452173304437594</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08362342237631225</v>
+      </c>
+      <c r="C39">
+        <v>11.78651379977593</v>
+      </c>
+      <c r="D39">
+        <v>16.30171379977593</v>
+      </c>
+      <c r="E39">
+        <v>2.8852</v>
+      </c>
+      <c r="F39">
+        <v>6.6452</v>
+      </c>
+      <c r="G39">
+        <v>2.13</v>
+      </c>
+      <c r="H39">
+        <v>14.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3.125</v>
+      </c>
+      <c r="K39">
+        <v>1.06</v>
+      </c>
+      <c r="L39">
+        <v>2.065</v>
+      </c>
+      <c r="M39">
+        <v>0.3289374</v>
+      </c>
+      <c r="N39">
+        <v>1.7360626</v>
+      </c>
+      <c r="O39">
+        <v>0.460056589</v>
+      </c>
+      <c r="P39">
+        <v>1.276006011</v>
+      </c>
+      <c r="Q39">
+        <v>2.336006011</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1113680910735115</v>
+      </c>
+      <c r="T39">
+        <v>1.57756719725025</v>
+      </c>
+      <c r="U39">
+        <v>0.0495</v>
+      </c>
+      <c r="V39">
+        <v>0.265</v>
+      </c>
+      <c r="W39">
+        <v>0.0363825</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.277790242155498</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08385594460005279</v>
+      </c>
+      <c r="C40">
+        <v>11.56601319815188</v>
+      </c>
+      <c r="D40">
+        <v>16.26081319815188</v>
+      </c>
+      <c r="E40">
+        <v>3.064800000000001</v>
+      </c>
+      <c r="F40">
+        <v>6.824800000000001</v>
+      </c>
+      <c r="G40">
+        <v>2.13</v>
+      </c>
+      <c r="H40">
+        <v>14.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3.125</v>
+      </c>
+      <c r="K40">
+        <v>1.06</v>
+      </c>
+      <c r="L40">
+        <v>2.065</v>
+      </c>
+      <c r="M40">
+        <v>0.34738232</v>
+      </c>
+      <c r="N40">
+        <v>1.71761768</v>
+      </c>
+      <c r="O40">
+        <v>0.4551686852</v>
+      </c>
+      <c r="P40">
+        <v>1.2624489948</v>
+      </c>
+      <c r="Q40">
+        <v>2.3224489948</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1123218945162142</v>
+      </c>
+      <c r="T40">
+        <v>1.598302054700308</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.265</v>
+      </c>
+      <c r="W40">
+        <v>0.0374115</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.944459119278148</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08370773682379332</v>
+      </c>
+      <c r="C41">
+        <v>11.41245915376611</v>
+      </c>
+      <c r="D41">
+        <v>16.28685915376611</v>
+      </c>
+      <c r="E41">
+        <v>3.244400000000001</v>
+      </c>
+      <c r="F41">
+        <v>7.0044</v>
+      </c>
+      <c r="G41">
+        <v>2.13</v>
+      </c>
+      <c r="H41">
+        <v>14.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3.125</v>
+      </c>
+      <c r="K41">
+        <v>1.06</v>
+      </c>
+      <c r="L41">
+        <v>2.065</v>
+      </c>
+      <c r="M41">
+        <v>0.35652396</v>
+      </c>
+      <c r="N41">
+        <v>1.70847604</v>
+      </c>
+      <c r="O41">
+        <v>0.4527461506</v>
+      </c>
+      <c r="P41">
+        <v>1.2557298894</v>
+      </c>
+      <c r="Q41">
+        <v>2.3157298894</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1133069702029399</v>
+      </c>
+      <c r="T41">
+        <v>1.619716743542171</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.265</v>
+      </c>
+      <c r="W41">
+        <v>0.0374115</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.792037090578708</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08355952904753383</v>
+      </c>
+      <c r="C42">
+        <v>11.25898868209731</v>
+      </c>
+      <c r="D42">
+        <v>16.31298868209731</v>
+      </c>
+      <c r="E42">
+        <v>3.424000000000001</v>
+      </c>
+      <c r="F42">
+        <v>7.184000000000001</v>
+      </c>
+      <c r="G42">
+        <v>2.13</v>
+      </c>
+      <c r="H42">
+        <v>14.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3.125</v>
+      </c>
+      <c r="K42">
+        <v>1.06</v>
+      </c>
+      <c r="L42">
+        <v>2.065</v>
+      </c>
+      <c r="M42">
+        <v>0.3656656</v>
+      </c>
+      <c r="N42">
+        <v>1.6993344</v>
+      </c>
+      <c r="O42">
+        <v>0.450323616</v>
+      </c>
+      <c r="P42">
+        <v>1.249010784</v>
+      </c>
+      <c r="Q42">
+        <v>2.309010784</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1143248817458897</v>
+      </c>
+      <c r="T42">
+        <v>1.641845255345429</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.265</v>
+      </c>
+      <c r="W42">
+        <v>0.0374115</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.647236163314241</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08341132127127437</v>
+      </c>
+      <c r="C43">
+        <v>11.10560218602696</v>
+      </c>
+      <c r="D43">
+        <v>16.33920218602696</v>
+      </c>
+      <c r="E43">
+        <v>3.603600000000001</v>
+      </c>
+      <c r="F43">
+        <v>7.363600000000001</v>
+      </c>
+      <c r="G43">
+        <v>2.13</v>
+      </c>
+      <c r="H43">
+        <v>14.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3.125</v>
+      </c>
+      <c r="K43">
+        <v>1.06</v>
+      </c>
+      <c r="L43">
+        <v>2.065</v>
+      </c>
+      <c r="M43">
+        <v>0.37480724</v>
+      </c>
+      <c r="N43">
+        <v>1.69019276</v>
+      </c>
+      <c r="O43">
+        <v>0.4479010814</v>
+      </c>
+      <c r="P43">
+        <v>1.2422916786</v>
+      </c>
+      <c r="Q43">
+        <v>2.3022916786</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1153772987648718</v>
+      </c>
+      <c r="T43">
+        <v>1.664723886192866</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.265</v>
+      </c>
+      <c r="W43">
+        <v>0.0374115</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.509498695916332</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08326311349501492</v>
+      </c>
+      <c r="C44">
+        <v>10.95230007103031</v>
+      </c>
+      <c r="D44">
+        <v>16.36550007103031</v>
+      </c>
+      <c r="E44">
+        <v>3.7832</v>
+      </c>
+      <c r="F44">
+        <v>7.5432</v>
+      </c>
+      <c r="G44">
+        <v>2.13</v>
+      </c>
+      <c r="H44">
+        <v>14.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>3.125</v>
+      </c>
+      <c r="K44">
+        <v>1.06</v>
+      </c>
+      <c r="L44">
+        <v>2.065</v>
+      </c>
+      <c r="M44">
+        <v>0.38394888</v>
+      </c>
+      <c r="N44">
+        <v>1.68105112</v>
+      </c>
+      <c r="O44">
+        <v>0.4454785468</v>
+      </c>
+      <c r="P44">
+        <v>1.2355725732</v>
+      </c>
+      <c r="Q44">
+        <v>2.2955725732</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1164660060258878</v>
+      </c>
+      <c r="T44">
+        <v>1.688391435345386</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.265</v>
+      </c>
+      <c r="W44">
+        <v>0.0374115</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.378320155537373</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08311490571875543</v>
+      </c>
+      <c r="C45">
+        <v>10.79908274519724</v>
+      </c>
+      <c r="D45">
+        <v>16.39188274519724</v>
+      </c>
+      <c r="E45">
+        <v>3.962800000000001</v>
+      </c>
+      <c r="F45">
+        <v>7.7228</v>
+      </c>
+      <c r="G45">
+        <v>2.13</v>
+      </c>
+      <c r="H45">
+        <v>14.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3.125</v>
+      </c>
+      <c r="K45">
+        <v>1.06</v>
+      </c>
+      <c r="L45">
+        <v>2.065</v>
+      </c>
+      <c r="M45">
+        <v>0.39309052</v>
+      </c>
+      <c r="N45">
+        <v>1.67190948</v>
+      </c>
+      <c r="O45">
+        <v>0.4430560122</v>
+      </c>
+      <c r="P45">
+        <v>1.2288534678</v>
+      </c>
+      <c r="Q45">
+        <v>2.2888534678</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1175929135416762</v>
+      </c>
+      <c r="T45">
+        <v>1.712889424819048</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.265</v>
+      </c>
+      <c r="W45">
+        <v>0.0374115</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.253242942617899</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08296669794249598</v>
+      </c>
+      <c r="C46">
+        <v>10.6459506192534</v>
+      </c>
+      <c r="D46">
+        <v>16.4183506192534</v>
+      </c>
+      <c r="E46">
+        <v>4.1424</v>
+      </c>
+      <c r="F46">
+        <v>7.9024</v>
+      </c>
+      <c r="G46">
+        <v>2.13</v>
+      </c>
+      <c r="H46">
+        <v>14.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>3.125</v>
+      </c>
+      <c r="K46">
+        <v>1.06</v>
+      </c>
+      <c r="L46">
+        <v>2.065</v>
+      </c>
+      <c r="M46">
+        <v>0.40223216</v>
+      </c>
+      <c r="N46">
+        <v>1.66276784</v>
+      </c>
+      <c r="O46">
+        <v>0.4406334776</v>
+      </c>
+      <c r="P46">
+        <v>1.2221343624</v>
+      </c>
+      <c r="Q46">
+        <v>2.2821343624</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1187600677544571</v>
+      </c>
+      <c r="T46">
+        <v>1.738262342488198</v>
+      </c>
+      <c r="U46">
+        <v>0.0509</v>
+      </c>
+      <c r="V46">
+        <v>0.265</v>
+      </c>
+      <c r="W46">
+        <v>0.0374115</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.133851057558401</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08281849016623652</v>
+      </c>
+      <c r="C47">
+        <v>10.49290410658152</v>
+      </c>
+      <c r="D47">
+        <v>16.44490410658152</v>
+      </c>
+      <c r="E47">
+        <v>4.322000000000001</v>
+      </c>
+      <c r="F47">
+        <v>8.082000000000001</v>
+      </c>
+      <c r="G47">
+        <v>2.13</v>
+      </c>
+      <c r="H47">
+        <v>14.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3.125</v>
+      </c>
+      <c r="K47">
+        <v>1.06</v>
+      </c>
+      <c r="L47">
+        <v>2.065</v>
+      </c>
+      <c r="M47">
+        <v>0.4113738000000001</v>
+      </c>
+      <c r="N47">
+        <v>1.6536262</v>
+      </c>
+      <c r="O47">
+        <v>0.438210943</v>
+      </c>
+      <c r="P47">
+        <v>1.215415257</v>
+      </c>
+      <c r="Q47">
+        <v>2.275415257</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1199696639386118</v>
+      </c>
+      <c r="T47">
+        <v>1.764557911708953</v>
+      </c>
+      <c r="U47">
+        <v>0.0509</v>
+      </c>
+      <c r="V47">
+        <v>0.265</v>
+      </c>
+      <c r="W47">
+        <v>0.0374115</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.019765478501547</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.08267028238997703</v>
+      </c>
+      <c r="C48">
+        <v>10.33994362324293</v>
+      </c>
+      <c r="D48">
+        <v>16.47154362324293</v>
+      </c>
+      <c r="E48">
+        <v>4.501600000000002</v>
+      </c>
+      <c r="F48">
+        <v>8.261600000000001</v>
+      </c>
+      <c r="G48">
+        <v>2.13</v>
+      </c>
+      <c r="H48">
+        <v>14.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>3.125</v>
+      </c>
+      <c r="K48">
+        <v>1.06</v>
+      </c>
+      <c r="L48">
+        <v>2.065</v>
+      </c>
+      <c r="M48">
+        <v>0.4205154400000001</v>
+      </c>
+      <c r="N48">
+        <v>1.64448456</v>
+      </c>
+      <c r="O48">
+        <v>0.4357884084</v>
+      </c>
+      <c r="P48">
+        <v>1.2086961516</v>
+      </c>
+      <c r="Q48">
+        <v>2.2686961516</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1212240599814389</v>
+      </c>
+      <c r="T48">
+        <v>1.791827390900847</v>
+      </c>
+      <c r="U48">
+        <v>0.0509</v>
+      </c>
+      <c r="V48">
+        <v>0.265</v>
+      </c>
+      <c r="W48">
+        <v>0.0374115</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.910640142012383</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.08252207461371756</v>
+      </c>
+      <c r="C49">
+        <v>10.18706958799927</v>
+      </c>
+      <c r="D49">
+        <v>16.49826958799927</v>
+      </c>
+      <c r="E49">
+        <v>4.6812</v>
+      </c>
+      <c r="F49">
+        <v>8.4412</v>
+      </c>
+      <c r="G49">
+        <v>2.13</v>
+      </c>
+      <c r="H49">
+        <v>14.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>3.125</v>
+      </c>
+      <c r="K49">
+        <v>1.06</v>
+      </c>
+      <c r="L49">
+        <v>2.065</v>
+      </c>
+      <c r="M49">
+        <v>0.42965708</v>
+      </c>
+      <c r="N49">
+        <v>1.63534292</v>
+      </c>
+      <c r="O49">
+        <v>0.4333658738</v>
+      </c>
+      <c r="P49">
+        <v>1.2019770462</v>
+      </c>
+      <c r="Q49">
+        <v>2.2619770462</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1225257917239954</v>
+      </c>
+      <c r="T49">
+        <v>1.820125907043379</v>
+      </c>
+      <c r="U49">
+        <v>0.0509</v>
+      </c>
+      <c r="V49">
+        <v>0.265</v>
+      </c>
+      <c r="W49">
+        <v>0.0374115</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>4.806158436863184</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.08237386683745811</v>
+      </c>
+      <c r="C50">
+        <v>10.03428242233446</v>
+      </c>
+      <c r="D50">
+        <v>16.52508242233446</v>
+      </c>
+      <c r="E50">
+        <v>4.860800000000001</v>
+      </c>
+      <c r="F50">
+        <v>8.620800000000001</v>
+      </c>
+      <c r="G50">
+        <v>2.13</v>
+      </c>
+      <c r="H50">
+        <v>14.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3.125</v>
+      </c>
+      <c r="K50">
+        <v>1.06</v>
+      </c>
+      <c r="L50">
+        <v>2.065</v>
+      </c>
+      <c r="M50">
+        <v>0.43879872</v>
+      </c>
+      <c r="N50">
+        <v>1.62620128</v>
+      </c>
+      <c r="O50">
+        <v>0.4309433392</v>
+      </c>
+      <c r="P50">
+        <v>1.1952579408</v>
+      </c>
+      <c r="Q50">
+        <v>2.2552579408</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1238775900720348</v>
+      </c>
+      <c r="T50">
+        <v>1.84951282765293</v>
+      </c>
+      <c r="U50">
+        <v>0.0509</v>
+      </c>
+      <c r="V50">
+        <v>0.265</v>
+      </c>
+      <c r="W50">
+        <v>0.0374115</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.706030136095201</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.08222565906119862</v>
+      </c>
+      <c r="C51">
+        <v>9.881582550476853</v>
+      </c>
+      <c r="D51">
+        <v>16.55198255047685</v>
+      </c>
+      <c r="E51">
+        <v>5.0404</v>
+      </c>
+      <c r="F51">
+        <v>8.8004</v>
+      </c>
+      <c r="G51">
+        <v>2.13</v>
+      </c>
+      <c r="H51">
+        <v>14.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3.125</v>
+      </c>
+      <c r="K51">
+        <v>1.06</v>
+      </c>
+      <c r="L51">
+        <v>2.065</v>
+      </c>
+      <c r="M51">
+        <v>0.44794036</v>
+      </c>
+      <c r="N51">
+        <v>1.61705964</v>
+      </c>
+      <c r="O51">
+        <v>0.4285208046</v>
+      </c>
+      <c r="P51">
+        <v>1.1885388354</v>
+      </c>
+      <c r="Q51">
+        <v>2.2485388354</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1252824001199973</v>
+      </c>
+      <c r="T51">
+        <v>1.880052176521681</v>
+      </c>
+      <c r="U51">
+        <v>0.0509</v>
+      </c>
+      <c r="V51">
+        <v>0.265</v>
+      </c>
+      <c r="W51">
+        <v>0.0374115</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.609988704746319</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.08207745128493915</v>
+      </c>
+      <c r="C52">
+        <v>9.728970399421598</v>
+      </c>
+      <c r="D52">
+        <v>16.5789703994216</v>
+      </c>
+      <c r="E52">
+        <v>5.220000000000001</v>
+      </c>
+      <c r="F52">
+        <v>8.98</v>
+      </c>
+      <c r="G52">
+        <v>2.13</v>
+      </c>
+      <c r="H52">
+        <v>14.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3.125</v>
+      </c>
+      <c r="K52">
+        <v>1.06</v>
+      </c>
+      <c r="L52">
+        <v>2.065</v>
+      </c>
+      <c r="M52">
+        <v>0.457082</v>
+      </c>
+      <c r="N52">
+        <v>1.607918</v>
+      </c>
+      <c r="O52">
+        <v>0.42609827</v>
+      </c>
+      <c r="P52">
+        <v>1.18181973</v>
+      </c>
+      <c r="Q52">
+        <v>2.24181973</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1267434025698783</v>
+      </c>
+      <c r="T52">
+        <v>1.911813099345181</v>
+      </c>
+      <c r="U52">
+        <v>0.0509</v>
+      </c>
+      <c r="V52">
+        <v>0.265</v>
+      </c>
+      <c r="W52">
+        <v>0.0374115</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.517788930651393</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.0829038535086797</v>
+      </c>
+      <c r="C53">
+        <v>9.399999596203855</v>
+      </c>
+      <c r="D53">
+        <v>16.42959959620386</v>
+      </c>
+      <c r="E53">
+        <v>5.399600000000001</v>
+      </c>
+      <c r="F53">
+        <v>9.159600000000001</v>
+      </c>
+      <c r="G53">
+        <v>2.13</v>
+      </c>
+      <c r="H53">
+        <v>14.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>3.125</v>
+      </c>
+      <c r="K53">
+        <v>1.06</v>
+      </c>
+      <c r="L53">
+        <v>2.065</v>
+      </c>
+      <c r="M53">
+        <v>0.4900386</v>
+      </c>
+      <c r="N53">
+        <v>1.5749614</v>
+      </c>
+      <c r="O53">
+        <v>0.417364771</v>
+      </c>
+      <c r="P53">
+        <v>1.157596629</v>
+      </c>
+      <c r="Q53">
+        <v>2.217596629</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1282640377728157</v>
+      </c>
+      <c r="T53">
+        <v>1.944870386365559</v>
+      </c>
+      <c r="U53">
+        <v>0.0535</v>
+      </c>
+      <c r="V53">
+        <v>0.265</v>
+      </c>
+      <c r="W53">
+        <v>0.0393225</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.213953757928456</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.08277475573242023</v>
+      </c>
+      <c r="C54">
+        <v>9.243556159516965</v>
+      </c>
+      <c r="D54">
+        <v>16.45275615951697</v>
+      </c>
+      <c r="E54">
+        <v>5.5792</v>
+      </c>
+      <c r="F54">
+        <v>9.3392</v>
+      </c>
+      <c r="G54">
+        <v>2.13</v>
+      </c>
+      <c r="H54">
+        <v>14.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>3.125</v>
+      </c>
+      <c r="K54">
+        <v>1.06</v>
+      </c>
+      <c r="L54">
+        <v>2.065</v>
+      </c>
+      <c r="M54">
+        <v>0.4996472</v>
+      </c>
+      <c r="N54">
+        <v>1.5653528</v>
+      </c>
+      <c r="O54">
+        <v>0.414818492</v>
+      </c>
+      <c r="P54">
+        <v>1.150534308</v>
+      </c>
+      <c r="Q54">
+        <v>2.210534308</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1298480327758755</v>
+      </c>
+      <c r="T54">
+        <v>1.979305060345119</v>
+      </c>
+      <c r="U54">
+        <v>0.0535</v>
+      </c>
+      <c r="V54">
+        <v>0.265</v>
+      </c>
+      <c r="W54">
+        <v>0.0393225</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.132916185660601</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
         <v>0.53</v>
       </c>
-      <c r="V5">
-        <v>0.05497925311203319</v>
-      </c>
-      <c r="W5">
-        <v>-1.281553398058253</v>
-      </c>
-      <c r="X5">
-        <v>0.1060288183648894</v>
-      </c>
-      <c r="Y5">
-        <v>-1.387582216423142</v>
-      </c>
-      <c r="Z5">
-        <v>3.141809290953545</v>
-      </c>
-      <c r="AA5">
-        <v>-0.4034229828850855</v>
-      </c>
-      <c r="AB5">
-        <v>0.1037869667101505</v>
-      </c>
-      <c r="AC5">
-        <v>-0.507209949595236</v>
-      </c>
-      <c r="AD5">
-        <v>0.422</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0.422</v>
-      </c>
-      <c r="AG5">
-        <v>-0.108</v>
-      </c>
-      <c r="AH5">
-        <v>0.04193997217253031</v>
-      </c>
-      <c r="AI5">
-        <v>0.1660110149488591</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.01133025597985733</v>
-      </c>
-      <c r="AK5">
-        <v>-0.05367793240556662</v>
-      </c>
-      <c r="AL5">
-        <v>0.06</v>
-      </c>
-      <c r="AM5">
-        <v>0.06</v>
-      </c>
-      <c r="AN5">
-        <v>-1.708502024291498</v>
-      </c>
-      <c r="AO5">
-        <v>-5.500000000000001</v>
-      </c>
-      <c r="AP5">
-        <v>0.4372469635627532</v>
-      </c>
-      <c r="AQ5">
-        <v>-5.500000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CE Brands Inc. (TSXV:CEBI)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Electronics (Consumer &amp; Office)</t>
-        </is>
-      </c>
-      <c r="G6">
-        <v>-0.9352220520673813</v>
-      </c>
-      <c r="H6">
-        <v>-0.9816232771822359</v>
-      </c>
-      <c r="I6">
-        <v>-0.9709035222052067</v>
-      </c>
-      <c r="J6">
-        <v>-0.9709035222052067</v>
-      </c>
-      <c r="K6">
-        <v>-7.46</v>
-      </c>
-      <c r="L6">
-        <v>-1.142419601837672</v>
-      </c>
-      <c r="M6">
-        <v>10.1</v>
-      </c>
-      <c r="N6">
-        <v>4.926829268292683</v>
-      </c>
-      <c r="O6">
-        <v>-1.353887399463807</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>10.1</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>0.251</v>
-      </c>
-      <c r="V6">
-        <v>0.1224390243902439</v>
-      </c>
-      <c r="W6">
-        <v>-1.12012012012012</v>
-      </c>
-      <c r="X6">
-        <v>0.2641602698393573</v>
-      </c>
-      <c r="Y6">
-        <v>-1.384280389959477</v>
-      </c>
-      <c r="Z6">
-        <v>5.207336523125991</v>
-      </c>
-      <c r="AA6">
-        <v>-5.05582137161084</v>
-      </c>
-      <c r="AB6">
-        <v>0.1504974149397133</v>
-      </c>
-      <c r="AC6">
-        <v>-5.206318786550553</v>
-      </c>
-      <c r="AD6">
-        <v>6.73</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>6.73</v>
-      </c>
-      <c r="AG6">
-        <v>6.479</v>
-      </c>
-      <c r="AH6">
-        <v>0.7665148063781321</v>
-      </c>
-      <c r="AI6">
-        <v>0.9349819394276188</v>
-      </c>
-      <c r="AJ6">
-        <v>0.7596435689998827</v>
-      </c>
-      <c r="AK6">
-        <v>0.9326327911328631</v>
-      </c>
-      <c r="AL6">
-        <v>1.15</v>
-      </c>
-      <c r="AM6">
-        <v>1.15</v>
-      </c>
-      <c r="AN6">
-        <v>-1.121666666666667</v>
-      </c>
-      <c r="AO6">
-        <v>-5.51304347826087</v>
-      </c>
-      <c r="AP6">
-        <v>-1.079833333333333</v>
-      </c>
-      <c r="AQ6">
-        <v>-5.51304347826087</v>
+      <c r="B55">
+        <v>0.08264565795616076</v>
+      </c>
+      <c r="C55">
+        <v>9.087178090615572</v>
+      </c>
+      <c r="D55">
+        <v>16.47597809061557</v>
+      </c>
+      <c r="E55">
+        <v>5.758800000000001</v>
+      </c>
+      <c r="F55">
+        <v>9.518800000000001</v>
+      </c>
+      <c r="G55">
+        <v>2.13</v>
+      </c>
+      <c r="H55">
+        <v>14.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>3.125</v>
+      </c>
+      <c r="K55">
+        <v>1.06</v>
+      </c>
+      <c r="L55">
+        <v>2.065</v>
+      </c>
+      <c r="M55">
+        <v>0.5092558</v>
+      </c>
+      <c r="N55">
+        <v>1.5557442</v>
+      </c>
+      <c r="O55">
+        <v>0.412272213</v>
+      </c>
+      <c r="P55">
+        <v>1.143471987</v>
+      </c>
+      <c r="Q55">
+        <v>2.203471987</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1314994318216186</v>
+      </c>
+      <c r="T55">
+        <v>2.015205039600405</v>
+      </c>
+      <c r="U55">
+        <v>0.0535</v>
+      </c>
+      <c r="V55">
+        <v>0.265</v>
+      </c>
+      <c r="W55">
+        <v>0.0393225</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.05493663498776</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.08358819017990129</v>
+      </c>
+      <c r="C56">
+        <v>8.739529091255585</v>
+      </c>
+      <c r="D56">
+        <v>16.30792909125559</v>
+      </c>
+      <c r="E56">
+        <v>5.938400000000001</v>
+      </c>
+      <c r="F56">
+        <v>9.698400000000001</v>
+      </c>
+      <c r="G56">
+        <v>2.13</v>
+      </c>
+      <c r="H56">
+        <v>14.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3.125</v>
+      </c>
+      <c r="K56">
+        <v>1.06</v>
+      </c>
+      <c r="L56">
+        <v>2.065</v>
+      </c>
+      <c r="M56">
+        <v>0.5450500800000001</v>
+      </c>
+      <c r="N56">
+        <v>1.51994992</v>
+      </c>
+      <c r="O56">
+        <v>0.4027867287999999</v>
+      </c>
+      <c r="P56">
+        <v>1.1171631912</v>
+      </c>
+      <c r="Q56">
+        <v>2.1771631912</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1332226308258724</v>
+      </c>
+      <c r="T56">
+        <v>2.052665887518965</v>
+      </c>
+      <c r="U56">
+        <v>0.0562</v>
+      </c>
+      <c r="V56">
+        <v>0.265</v>
+      </c>
+      <c r="W56">
+        <v>0.041307</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.788642687659085</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08347893740364182</v>
+      </c>
+      <c r="C57">
+        <v>8.579232480871939</v>
+      </c>
+      <c r="D57">
+        <v>16.32723248087194</v>
+      </c>
+      <c r="E57">
+        <v>6.118000000000002</v>
+      </c>
+      <c r="F57">
+        <v>9.878000000000002</v>
+      </c>
+      <c r="G57">
+        <v>2.13</v>
+      </c>
+      <c r="H57">
+        <v>14.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>3.125</v>
+      </c>
+      <c r="K57">
+        <v>1.06</v>
+      </c>
+      <c r="L57">
+        <v>2.065</v>
+      </c>
+      <c r="M57">
+        <v>0.5551436000000001</v>
+      </c>
+      <c r="N57">
+        <v>1.5098564</v>
+      </c>
+      <c r="O57">
+        <v>0.400111946</v>
+      </c>
+      <c r="P57">
+        <v>1.109744454</v>
+      </c>
+      <c r="Q57">
+        <v>2.169744454</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1350224164525374</v>
+      </c>
+      <c r="T57">
+        <v>2.091791662011682</v>
+      </c>
+      <c r="U57">
+        <v>0.0562</v>
+      </c>
+      <c r="V57">
+        <v>0.265</v>
+      </c>
+      <c r="W57">
+        <v>0.041307</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>3.719758275156193</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08336968462738235</v>
+      </c>
+      <c r="C58">
+        <v>8.418981622764452</v>
+      </c>
+      <c r="D58">
+        <v>16.34658162276445</v>
+      </c>
+      <c r="E58">
+        <v>6.297600000000001</v>
+      </c>
+      <c r="F58">
+        <v>10.0576</v>
+      </c>
+      <c r="G58">
+        <v>2.13</v>
+      </c>
+      <c r="H58">
+        <v>14.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>3.125</v>
+      </c>
+      <c r="K58">
+        <v>1.06</v>
+      </c>
+      <c r="L58">
+        <v>2.065</v>
+      </c>
+      <c r="M58">
+        <v>0.56523712</v>
+      </c>
+      <c r="N58">
+        <v>1.49976288</v>
+      </c>
+      <c r="O58">
+        <v>0.3974371632</v>
+      </c>
+      <c r="P58">
+        <v>1.1023257168</v>
+      </c>
+      <c r="Q58">
+        <v>2.1623257168</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1369040105167781</v>
+      </c>
+      <c r="T58">
+        <v>2.132695880799524</v>
+      </c>
+      <c r="U58">
+        <v>0.0562</v>
+      </c>
+      <c r="V58">
+        <v>0.265</v>
+      </c>
+      <c r="W58">
+        <v>0.041307</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>3.65333402024269</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08326043185112289</v>
+      </c>
+      <c r="C59">
+        <v>8.258776679786987</v>
+      </c>
+      <c r="D59">
+        <v>16.36597667978699</v>
+      </c>
+      <c r="E59">
+        <v>6.477200000000002</v>
+      </c>
+      <c r="F59">
+        <v>10.2372</v>
+      </c>
+      <c r="G59">
+        <v>2.13</v>
+      </c>
+      <c r="H59">
+        <v>14.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>3.125</v>
+      </c>
+      <c r="K59">
+        <v>1.06</v>
+      </c>
+      <c r="L59">
+        <v>2.065</v>
+      </c>
+      <c r="M59">
+        <v>0.5753306400000001</v>
+      </c>
+      <c r="N59">
+        <v>1.48966936</v>
+      </c>
+      <c r="O59">
+        <v>0.3947623803999999</v>
+      </c>
+      <c r="P59">
+        <v>1.0949069796</v>
+      </c>
+      <c r="Q59">
+        <v>2.1549069796</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1388731205840067</v>
+      </c>
+      <c r="T59">
+        <v>2.175502621391451</v>
+      </c>
+      <c r="U59">
+        <v>0.0562</v>
+      </c>
+      <c r="V59">
+        <v>0.265</v>
+      </c>
+      <c r="W59">
+        <v>0.041307</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.589240440940186</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.08315117907486341</v>
+      </c>
+      <c r="C60">
+        <v>8.098617815567236</v>
+      </c>
+      <c r="D60">
+        <v>16.38541781556724</v>
+      </c>
+      <c r="E60">
+        <v>6.6568</v>
+      </c>
+      <c r="F60">
+        <v>10.4168</v>
+      </c>
+      <c r="G60">
+        <v>2.13</v>
+      </c>
+      <c r="H60">
+        <v>14.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3.125</v>
+      </c>
+      <c r="K60">
+        <v>1.06</v>
+      </c>
+      <c r="L60">
+        <v>2.065</v>
+      </c>
+      <c r="M60">
+        <v>0.58542416</v>
+      </c>
+      <c r="N60">
+        <v>1.47957584</v>
+      </c>
+      <c r="O60">
+        <v>0.3920875976</v>
+      </c>
+      <c r="P60">
+        <v>1.0874882424</v>
+      </c>
+      <c r="Q60">
+        <v>2.1474882424</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1409359977972938</v>
+      </c>
+      <c r="T60">
+        <v>2.22034777820204</v>
+      </c>
+      <c r="U60">
+        <v>0.0562</v>
+      </c>
+      <c r="V60">
+        <v>0.265</v>
+      </c>
+      <c r="W60">
+        <v>0.041307</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.527356985061908</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.08508008129860394</v>
+      </c>
+      <c r="C61">
+        <v>7.582428160195828</v>
+      </c>
+      <c r="D61">
+        <v>16.04882816019583</v>
+      </c>
+      <c r="E61">
+        <v>6.836399999999999</v>
+      </c>
+      <c r="F61">
+        <v>10.5964</v>
+      </c>
+      <c r="G61">
+        <v>2.13</v>
+      </c>
+      <c r="H61">
+        <v>14.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>3.125</v>
+      </c>
+      <c r="K61">
+        <v>1.06</v>
+      </c>
+      <c r="L61">
+        <v>2.065</v>
+      </c>
+      <c r="M61">
+        <v>0.6453207599999999</v>
+      </c>
+      <c r="N61">
+        <v>1.41967924</v>
+      </c>
+      <c r="O61">
+        <v>0.3762149986</v>
+      </c>
+      <c r="P61">
+        <v>1.0434642414</v>
+      </c>
+      <c r="Q61">
+        <v>2.1034642414</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1430995031673267</v>
+      </c>
+      <c r="T61">
+        <v>2.267380503637537</v>
+      </c>
+      <c r="U61">
+        <v>0.0609</v>
+      </c>
+      <c r="V61">
+        <v>0.265</v>
+      </c>
+      <c r="W61">
+        <v>0.0447615</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.199959040524281</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08500537352234448</v>
+      </c>
+      <c r="C62">
+        <v>7.415606894266801</v>
+      </c>
+      <c r="D62">
+        <v>16.0616068942668</v>
+      </c>
+      <c r="E62">
+        <v>7.016</v>
+      </c>
+      <c r="F62">
+        <v>10.776</v>
+      </c>
+      <c r="G62">
+        <v>2.13</v>
+      </c>
+      <c r="H62">
+        <v>14.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3.125</v>
+      </c>
+      <c r="K62">
+        <v>1.06</v>
+      </c>
+      <c r="L62">
+        <v>2.065</v>
+      </c>
+      <c r="M62">
+        <v>0.6562584</v>
+      </c>
+      <c r="N62">
+        <v>1.4087416</v>
+      </c>
+      <c r="O62">
+        <v>0.373316524</v>
+      </c>
+      <c r="P62">
+        <v>1.035425076</v>
+      </c>
+      <c r="Q62">
+        <v>2.095425076</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1453711838058612</v>
+      </c>
+      <c r="T62">
+        <v>2.316764865344809</v>
+      </c>
+      <c r="U62">
+        <v>0.0609</v>
+      </c>
+      <c r="V62">
+        <v>0.265</v>
+      </c>
+      <c r="W62">
+        <v>0.0447615</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.146626389848876</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08493066574608502</v>
+      </c>
+      <c r="C63">
+        <v>7.248805994456649</v>
+      </c>
+      <c r="D63">
+        <v>16.07440599445665</v>
+      </c>
+      <c r="E63">
+        <v>7.195600000000001</v>
+      </c>
+      <c r="F63">
+        <v>10.9556</v>
+      </c>
+      <c r="G63">
+        <v>2.13</v>
+      </c>
+      <c r="H63">
+        <v>14.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>3.125</v>
+      </c>
+      <c r="K63">
+        <v>1.06</v>
+      </c>
+      <c r="L63">
+        <v>2.065</v>
+      </c>
+      <c r="M63">
+        <v>0.6671960400000001</v>
+      </c>
+      <c r="N63">
+        <v>1.39780396</v>
+      </c>
+      <c r="O63">
+        <v>0.3704180494</v>
+      </c>
+      <c r="P63">
+        <v>1.0273859106</v>
+      </c>
+      <c r="Q63">
+        <v>2.0873859106</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1477593608873975</v>
+      </c>
+      <c r="T63">
+        <v>2.368681758421684</v>
+      </c>
+      <c r="U63">
+        <v>0.0609</v>
+      </c>
+      <c r="V63">
+        <v>0.265</v>
+      </c>
+      <c r="W63">
+        <v>0.0447615</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.095042350671025</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.08485595796982555</v>
+      </c>
+      <c r="C64">
+        <v>7.082025509491984</v>
+      </c>
+      <c r="D64">
+        <v>16.08722550949199</v>
+      </c>
+      <c r="E64">
+        <v>7.375200000000001</v>
+      </c>
+      <c r="F64">
+        <v>11.1352</v>
+      </c>
+      <c r="G64">
+        <v>2.13</v>
+      </c>
+      <c r="H64">
+        <v>14.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3.125</v>
+      </c>
+      <c r="K64">
+        <v>1.06</v>
+      </c>
+      <c r="L64">
+        <v>2.065</v>
+      </c>
+      <c r="M64">
+        <v>0.6781336800000001</v>
+      </c>
+      <c r="N64">
+        <v>1.38686632</v>
+      </c>
+      <c r="O64">
+        <v>0.3675195748</v>
+      </c>
+      <c r="P64">
+        <v>1.0193467452</v>
+      </c>
+      <c r="Q64">
+        <v>2.0793467452</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1502732314995409</v>
+      </c>
+      <c r="T64">
+        <v>2.423331119555237</v>
+      </c>
+      <c r="U64">
+        <v>0.0609</v>
+      </c>
+      <c r="V64">
+        <v>0.265</v>
+      </c>
+      <c r="W64">
+        <v>0.0447615</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>3.045122312756977</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.08908761519356606</v>
+      </c>
+      <c r="C65">
+        <v>6.207122356634466</v>
+      </c>
+      <c r="D65">
+        <v>15.39192235663447</v>
+      </c>
+      <c r="E65">
+        <v>7.5548</v>
+      </c>
+      <c r="F65">
+        <v>11.3148</v>
+      </c>
+      <c r="G65">
+        <v>2.13</v>
+      </c>
+      <c r="H65">
+        <v>14.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3.125</v>
+      </c>
+      <c r="K65">
+        <v>1.06</v>
+      </c>
+      <c r="L65">
+        <v>2.065</v>
+      </c>
+      <c r="M65">
+        <v>0.79429896</v>
+      </c>
+      <c r="N65">
+        <v>1.27070104</v>
+      </c>
+      <c r="O65">
+        <v>0.3367357756</v>
+      </c>
+      <c r="P65">
+        <v>0.9339652644000001</v>
+      </c>
+      <c r="Q65">
+        <v>1.9939652644</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.152922987009638</v>
+      </c>
+      <c r="T65">
+        <v>2.480934500209523</v>
+      </c>
+      <c r="U65">
+        <v>0.0702</v>
+      </c>
+      <c r="V65">
+        <v>0.265</v>
+      </c>
+      <c r="W65">
+        <v>0.051597</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.59977678933383</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.0890812624173066</v>
+      </c>
+      <c r="C66">
+        <v>6.028521130504457</v>
+      </c>
+      <c r="D66">
+        <v>15.39292113050446</v>
+      </c>
+      <c r="E66">
+        <v>7.734400000000001</v>
+      </c>
+      <c r="F66">
+        <v>11.4944</v>
+      </c>
+      <c r="G66">
+        <v>2.13</v>
+      </c>
+      <c r="H66">
+        <v>14.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>3.125</v>
+      </c>
+      <c r="K66">
+        <v>1.06</v>
+      </c>
+      <c r="L66">
+        <v>2.065</v>
+      </c>
+      <c r="M66">
+        <v>0.80690688</v>
+      </c>
+      <c r="N66">
+        <v>1.25809312</v>
+      </c>
+      <c r="O66">
+        <v>0.3333946768</v>
+      </c>
+      <c r="P66">
+        <v>0.9246984431999998</v>
+      </c>
+      <c r="Q66">
+        <v>1.9846984432</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.155719951159185</v>
+      </c>
+      <c r="T66">
+        <v>2.541738068677935</v>
+      </c>
+      <c r="U66">
+        <v>0.0702</v>
+      </c>
+      <c r="V66">
+        <v>0.265</v>
+      </c>
+      <c r="W66">
+        <v>0.051597</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.559155277000488</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.08907490964104714</v>
+      </c>
+      <c r="C67">
+        <v>5.849920034002698</v>
+      </c>
+      <c r="D67">
+        <v>15.3939200340027</v>
+      </c>
+      <c r="E67">
+        <v>7.914000000000001</v>
+      </c>
+      <c r="F67">
+        <v>11.674</v>
+      </c>
+      <c r="G67">
+        <v>2.13</v>
+      </c>
+      <c r="H67">
+        <v>14.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>3.125</v>
+      </c>
+      <c r="K67">
+        <v>1.06</v>
+      </c>
+      <c r="L67">
+        <v>2.065</v>
+      </c>
+      <c r="M67">
+        <v>0.8195148000000001</v>
+      </c>
+      <c r="N67">
+        <v>1.2454852</v>
+      </c>
+      <c r="O67">
+        <v>0.330053578</v>
+      </c>
+      <c r="P67">
+        <v>0.9154316219999998</v>
+      </c>
+      <c r="Q67">
+        <v>1.975431622</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1586767418315632</v>
+      </c>
+      <c r="T67">
+        <v>2.606016126773114</v>
+      </c>
+      <c r="U67">
+        <v>0.0702</v>
+      </c>
+      <c r="V67">
+        <v>0.265</v>
+      </c>
+      <c r="W67">
+        <v>0.051597</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.519783657354327</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.09134852686478767</v>
+      </c>
+      <c r="C68">
+        <v>5.320910821418257</v>
+      </c>
+      <c r="D68">
+        <v>15.04451082141826</v>
+      </c>
+      <c r="E68">
+        <v>8.093600000000002</v>
+      </c>
+      <c r="F68">
+        <v>11.8536</v>
+      </c>
+      <c r="G68">
+        <v>2.13</v>
+      </c>
+      <c r="H68">
+        <v>14.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>3.125</v>
+      </c>
+      <c r="K68">
+        <v>1.06</v>
+      </c>
+      <c r="L68">
+        <v>2.065</v>
+      </c>
+      <c r="M68">
+        <v>0.8878346400000001</v>
+      </c>
+      <c r="N68">
+        <v>1.17716536</v>
+      </c>
+      <c r="O68">
+        <v>0.3119488204</v>
+      </c>
+      <c r="P68">
+        <v>0.8652165395999998</v>
+      </c>
+      <c r="Q68">
+        <v>1.9252165396</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1618074613670226</v>
+      </c>
+      <c r="T68">
+        <v>2.674075247109186</v>
+      </c>
+      <c r="U68">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.265</v>
+      </c>
+      <c r="W68">
+        <v>0.0550515</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.325883567687784</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09137671908852819</v>
+      </c>
+      <c r="C69">
+        <v>5.137077775638684</v>
+      </c>
+      <c r="D69">
+        <v>15.04027777563868</v>
+      </c>
+      <c r="E69">
+        <v>8.273200000000001</v>
+      </c>
+      <c r="F69">
+        <v>12.0332</v>
+      </c>
+      <c r="G69">
+        <v>2.13</v>
+      </c>
+      <c r="H69">
+        <v>14.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>3.125</v>
+      </c>
+      <c r="K69">
+        <v>1.06</v>
+      </c>
+      <c r="L69">
+        <v>2.065</v>
+      </c>
+      <c r="M69">
+        <v>0.90128668</v>
+      </c>
+      <c r="N69">
+        <v>1.16371332</v>
+      </c>
+      <c r="O69">
+        <v>0.3083840298</v>
+      </c>
+      <c r="P69">
+        <v>0.8553292901999998</v>
+      </c>
+      <c r="Q69">
+        <v>1.9153292902</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1651279214803885</v>
+      </c>
+      <c r="T69">
+        <v>2.746259162617141</v>
+      </c>
+      <c r="U69">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V69">
+        <v>0.265</v>
+      </c>
+      <c r="W69">
+        <v>0.0550515</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.291168887573042</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09140491131226874</v>
+      </c>
+      <c r="C70">
+        <v>4.953247111277342</v>
+      </c>
+      <c r="D70">
+        <v>15.03604711127734</v>
+      </c>
+      <c r="E70">
+        <v>8.452800000000002</v>
+      </c>
+      <c r="F70">
+        <v>12.2128</v>
+      </c>
+      <c r="G70">
+        <v>2.13</v>
+      </c>
+      <c r="H70">
+        <v>14.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>3.125</v>
+      </c>
+      <c r="K70">
+        <v>1.06</v>
+      </c>
+      <c r="L70">
+        <v>2.065</v>
+      </c>
+      <c r="M70">
+        <v>0.91473872</v>
+      </c>
+      <c r="N70">
+        <v>1.15026128</v>
+      </c>
+      <c r="O70">
+        <v>0.3048192392</v>
+      </c>
+      <c r="P70">
+        <v>0.8454420408000001</v>
+      </c>
+      <c r="Q70">
+        <v>1.9054420408</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1686559103508398</v>
+      </c>
+      <c r="T70">
+        <v>2.822954572844344</v>
+      </c>
+      <c r="U70">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V70">
+        <v>0.265</v>
+      </c>
+      <c r="W70">
+        <v>0.0550515</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.257475227461673</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09143310353600927</v>
+      </c>
+      <c r="C71">
+        <v>4.769418826325211</v>
+      </c>
+      <c r="D71">
+        <v>15.03181882632521</v>
+      </c>
+      <c r="E71">
+        <v>8.632400000000002</v>
+      </c>
+      <c r="F71">
+        <v>12.3924</v>
+      </c>
+      <c r="G71">
+        <v>2.13</v>
+      </c>
+      <c r="H71">
+        <v>14.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>3.125</v>
+      </c>
+      <c r="K71">
+        <v>1.06</v>
+      </c>
+      <c r="L71">
+        <v>2.065</v>
+      </c>
+      <c r="M71">
+        <v>0.9281907600000001</v>
+      </c>
+      <c r="N71">
+        <v>1.13680924</v>
+      </c>
+      <c r="O71">
+        <v>0.3012544485999999</v>
+      </c>
+      <c r="P71">
+        <v>0.8355547913999999</v>
+      </c>
+      <c r="Q71">
+        <v>1.8955547914</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1724115114064815</v>
+      </c>
+      <c r="T71">
+        <v>2.904598074053946</v>
+      </c>
+      <c r="U71">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V71">
+        <v>0.265</v>
+      </c>
+      <c r="W71">
+        <v>0.0550515</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.22475819517962</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09146129575974979</v>
+      </c>
+      <c r="C72">
+        <v>4.585592918775513</v>
+      </c>
+      <c r="D72">
+        <v>15.02759291877551</v>
+      </c>
+      <c r="E72">
+        <v>8.812000000000001</v>
+      </c>
+      <c r="F72">
+        <v>12.572</v>
+      </c>
+      <c r="G72">
+        <v>2.13</v>
+      </c>
+      <c r="H72">
+        <v>14.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>3.125</v>
+      </c>
+      <c r="K72">
+        <v>1.06</v>
+      </c>
+      <c r="L72">
+        <v>2.065</v>
+      </c>
+      <c r="M72">
+        <v>0.9416428</v>
+      </c>
+      <c r="N72">
+        <v>1.1233572</v>
+      </c>
+      <c r="O72">
+        <v>0.297689658</v>
+      </c>
+      <c r="P72">
+        <v>0.825667542</v>
+      </c>
+      <c r="Q72">
+        <v>1.885667542</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1764174858658327</v>
+      </c>
+      <c r="T72">
+        <v>2.991684475344188</v>
+      </c>
+      <c r="U72">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V72">
+        <v>0.265</v>
+      </c>
+      <c r="W72">
+        <v>0.0550515</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.192975935248483</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09148948798349033</v>
+      </c>
+      <c r="C73">
+        <v>4.401769386623723</v>
+      </c>
+      <c r="D73">
+        <v>15.02336938662372</v>
+      </c>
+      <c r="E73">
+        <v>8.9916</v>
+      </c>
+      <c r="F73">
+        <v>12.7516</v>
+      </c>
+      <c r="G73">
+        <v>2.13</v>
+      </c>
+      <c r="H73">
+        <v>14.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>3.125</v>
+      </c>
+      <c r="K73">
+        <v>1.06</v>
+      </c>
+      <c r="L73">
+        <v>2.065</v>
+      </c>
+      <c r="M73">
+        <v>0.9550948399999999</v>
+      </c>
+      <c r="N73">
+        <v>1.10990516</v>
+      </c>
+      <c r="O73">
+        <v>0.2941248674</v>
+      </c>
+      <c r="P73">
+        <v>0.8157802926</v>
+      </c>
+      <c r="Q73">
+        <v>1.8757802926</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1806997344258287</v>
+      </c>
+      <c r="T73">
+        <v>3.084776835344102</v>
+      </c>
+      <c r="U73">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V73">
+        <v>0.265</v>
+      </c>
+      <c r="W73">
+        <v>0.0550515</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>2.162088950244983</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09151768020723085</v>
+      </c>
+      <c r="C74">
+        <v>4.217948227867577</v>
+      </c>
+      <c r="D74">
+        <v>15.01914822786758</v>
+      </c>
+      <c r="E74">
+        <v>9.171200000000001</v>
+      </c>
+      <c r="F74">
+        <v>12.9312</v>
+      </c>
+      <c r="G74">
+        <v>2.13</v>
+      </c>
+      <c r="H74">
+        <v>14.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>3.125</v>
+      </c>
+      <c r="K74">
+        <v>1.06</v>
+      </c>
+      <c r="L74">
+        <v>2.065</v>
+      </c>
+      <c r="M74">
+        <v>0.96854688</v>
+      </c>
+      <c r="N74">
+        <v>1.09645312</v>
+      </c>
+      <c r="O74">
+        <v>0.2905600768</v>
+      </c>
+      <c r="P74">
+        <v>0.8058930432</v>
+      </c>
+      <c r="Q74">
+        <v>1.8658930432</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1852878578829673</v>
+      </c>
+      <c r="T74">
+        <v>3.184518649629724</v>
+      </c>
+      <c r="U74">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V74">
+        <v>0.265</v>
+      </c>
+      <c r="W74">
+        <v>0.0550515</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>2.132059937047136</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.0915458724309714</v>
+      </c>
+      <c r="C75">
+        <v>4.034129440507051</v>
+      </c>
+      <c r="D75">
+        <v>15.01492944050705</v>
+      </c>
+      <c r="E75">
+        <v>9.350800000000001</v>
+      </c>
+      <c r="F75">
+        <v>13.1108</v>
+      </c>
+      <c r="G75">
+        <v>2.13</v>
+      </c>
+      <c r="H75">
+        <v>14.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>3.125</v>
+      </c>
+      <c r="K75">
+        <v>1.06</v>
+      </c>
+      <c r="L75">
+        <v>2.065</v>
+      </c>
+      <c r="M75">
+        <v>0.98199892</v>
+      </c>
+      <c r="N75">
+        <v>1.08300108</v>
+      </c>
+      <c r="O75">
+        <v>0.2869952862</v>
+      </c>
+      <c r="P75">
+        <v>0.7960057937999998</v>
+      </c>
+      <c r="Q75">
+        <v>1.8560057938</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1902158423369311</v>
+      </c>
+      <c r="T75">
+        <v>3.291648746455023</v>
+      </c>
+      <c r="U75">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V75">
+        <v>0.265</v>
+      </c>
+      <c r="W75">
+        <v>0.0550515</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>2.102853636539641</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.09157406465471191</v>
+      </c>
+      <c r="C76">
+        <v>3.850313022544389</v>
+      </c>
+      <c r="D76">
+        <v>15.01071302254439</v>
+      </c>
+      <c r="E76">
+        <v>9.5304</v>
+      </c>
+      <c r="F76">
+        <v>13.2904</v>
+      </c>
+      <c r="G76">
+        <v>2.13</v>
+      </c>
+      <c r="H76">
+        <v>14.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>3.125</v>
+      </c>
+      <c r="K76">
+        <v>1.06</v>
+      </c>
+      <c r="L76">
+        <v>2.065</v>
+      </c>
+      <c r="M76">
+        <v>0.9954509599999999</v>
+      </c>
+      <c r="N76">
+        <v>1.06954904</v>
+      </c>
+      <c r="O76">
+        <v>0.2834304956000001</v>
+      </c>
+      <c r="P76">
+        <v>0.7861185444000001</v>
+      </c>
+      <c r="Q76">
+        <v>1.8461185444</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1955229025181228</v>
+      </c>
+      <c r="T76">
+        <v>3.407019619959191</v>
+      </c>
+      <c r="U76">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V76">
+        <v>0.265</v>
+      </c>
+      <c r="W76">
+        <v>0.0550515</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>2.074436695505322</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.09160225687845244</v>
+      </c>
+      <c r="C77">
+        <v>3.66649897198405</v>
+      </c>
+      <c r="D77">
+        <v>15.00649897198405</v>
+      </c>
+      <c r="E77">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="F77">
+        <v>13.47</v>
+      </c>
+      <c r="G77">
+        <v>2.13</v>
+      </c>
+      <c r="H77">
+        <v>14.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>3.125</v>
+      </c>
+      <c r="K77">
+        <v>1.06</v>
+      </c>
+      <c r="L77">
+        <v>2.065</v>
+      </c>
+      <c r="M77">
+        <v>1.008903</v>
+      </c>
+      <c r="N77">
+        <v>1.056097</v>
+      </c>
+      <c r="O77">
+        <v>0.279865705</v>
+      </c>
+      <c r="P77">
+        <v>0.7762312950000001</v>
+      </c>
+      <c r="Q77">
+        <v>1.836231295</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2012545275138098</v>
+      </c>
+      <c r="T77">
+        <v>3.531620163343692</v>
+      </c>
+      <c r="U77">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V77">
+        <v>0.265</v>
+      </c>
+      <c r="W77">
+        <v>0.0550515</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>2.046777539565251</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.09163044910219298</v>
+      </c>
+      <c r="C78">
+        <v>3.482687286832752</v>
+      </c>
+      <c r="D78">
+        <v>15.00228728683275</v>
+      </c>
+      <c r="E78">
+        <v>9.889600000000002</v>
+      </c>
+      <c r="F78">
+        <v>13.6496</v>
+      </c>
+      <c r="G78">
+        <v>2.13</v>
+      </c>
+      <c r="H78">
+        <v>14.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>3.125</v>
+      </c>
+      <c r="K78">
+        <v>1.06</v>
+      </c>
+      <c r="L78">
+        <v>2.065</v>
+      </c>
+      <c r="M78">
+        <v>1.02235504</v>
+      </c>
+      <c r="N78">
+        <v>1.04264496</v>
+      </c>
+      <c r="O78">
+        <v>0.2763009144</v>
+      </c>
+      <c r="P78">
+        <v>0.7663440455999999</v>
+      </c>
+      <c r="Q78">
+        <v>1.8263440456</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2074637879258041</v>
+      </c>
+      <c r="T78">
+        <v>3.666604085343568</v>
+      </c>
+      <c r="U78">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V78">
+        <v>0.265</v>
+      </c>
+      <c r="W78">
+        <v>0.0550515</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>2.019846256149918</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1008836263259335</v>
+      </c>
+      <c r="C79">
+        <v>2.037691111976773</v>
+      </c>
+      <c r="D79">
+        <v>13.73689111197677</v>
+      </c>
+      <c r="E79">
+        <v>10.0692</v>
+      </c>
+      <c r="F79">
+        <v>13.8292</v>
+      </c>
+      <c r="G79">
+        <v>2.13</v>
+      </c>
+      <c r="H79">
+        <v>14.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>3.125</v>
+      </c>
+      <c r="K79">
+        <v>1.06</v>
+      </c>
+      <c r="L79">
+        <v>2.065</v>
+      </c>
+      <c r="M79">
+        <v>1.26122304</v>
+      </c>
+      <c r="N79">
+        <v>0.80377696</v>
+      </c>
+      <c r="O79">
+        <v>0.2130008944</v>
+      </c>
+      <c r="P79">
+        <v>0.5907760656</v>
+      </c>
+      <c r="Q79">
+        <v>1.6507760656</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2142129840257979</v>
+      </c>
+      <c r="T79">
+        <v>3.813325739691259</v>
+      </c>
+      <c r="U79">
+        <v>0.0912</v>
+      </c>
+      <c r="V79">
+        <v>0.265</v>
+      </c>
+      <c r="W79">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>1.637299616727585</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.101031623549674</v>
+      </c>
+      <c r="C80">
+        <v>1.839584168922876</v>
+      </c>
+      <c r="D80">
+        <v>13.71838416892288</v>
+      </c>
+      <c r="E80">
+        <v>10.2488</v>
+      </c>
+      <c r="F80">
+        <v>14.0088</v>
+      </c>
+      <c r="G80">
+        <v>2.13</v>
+      </c>
+      <c r="H80">
+        <v>14.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>3.125</v>
+      </c>
+      <c r="K80">
+        <v>1.06</v>
+      </c>
+      <c r="L80">
+        <v>2.065</v>
+      </c>
+      <c r="M80">
+        <v>1.27760256</v>
+      </c>
+      <c r="N80">
+        <v>0.7873974399999999</v>
+      </c>
+      <c r="O80">
+        <v>0.2086603216</v>
+      </c>
+      <c r="P80">
+        <v>0.5787371183999999</v>
+      </c>
+      <c r="Q80">
+        <v>1.6387371184</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2215757434076093</v>
+      </c>
+      <c r="T80">
+        <v>3.973385726252376</v>
+      </c>
+      <c r="U80">
+        <v>0.0912</v>
+      </c>
+      <c r="V80">
+        <v>0.265</v>
+      </c>
+      <c r="W80">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>1.616308596000309</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1011796207734146</v>
+      </c>
+      <c r="C81">
+        <v>1.641527025509795</v>
+      </c>
+      <c r="D81">
+        <v>13.6999270255098</v>
+      </c>
+      <c r="E81">
+        <v>10.4284</v>
+      </c>
+      <c r="F81">
+        <v>14.1884</v>
+      </c>
+      <c r="G81">
+        <v>2.13</v>
+      </c>
+      <c r="H81">
+        <v>14.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>3.125</v>
+      </c>
+      <c r="K81">
+        <v>1.06</v>
+      </c>
+      <c r="L81">
+        <v>2.065</v>
+      </c>
+      <c r="M81">
+        <v>1.29398208</v>
+      </c>
+      <c r="N81">
+        <v>0.7710179199999998</v>
+      </c>
+      <c r="O81">
+        <v>0.2043197488</v>
+      </c>
+      <c r="P81">
+        <v>0.5666981711999999</v>
+      </c>
+      <c r="Q81">
+        <v>1.6266981712</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2296397179686409</v>
+      </c>
+      <c r="T81">
+        <v>4.148689521057411</v>
+      </c>
+      <c r="U81">
+        <v>0.0912</v>
+      </c>
+      <c r="V81">
+        <v>0.265</v>
+      </c>
+      <c r="W81">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>1.595848993519292</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1013276179971551</v>
+      </c>
+      <c r="C82">
+        <v>1.443519481001619</v>
+      </c>
+      <c r="D82">
+        <v>13.68151948100162</v>
+      </c>
+      <c r="E82">
+        <v>10.608</v>
+      </c>
+      <c r="F82">
+        <v>14.368</v>
+      </c>
+      <c r="G82">
+        <v>2.13</v>
+      </c>
+      <c r="H82">
+        <v>14.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>3.125</v>
+      </c>
+      <c r="K82">
+        <v>1.06</v>
+      </c>
+      <c r="L82">
+        <v>2.065</v>
+      </c>
+      <c r="M82">
+        <v>1.3103616</v>
+      </c>
+      <c r="N82">
+        <v>0.7546383999999997</v>
+      </c>
+      <c r="O82">
+        <v>0.1999791759999999</v>
+      </c>
+      <c r="P82">
+        <v>0.5546592239999998</v>
+      </c>
+      <c r="Q82">
+        <v>1.614659224</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2385100899857756</v>
+      </c>
+      <c r="T82">
+        <v>4.341523695342947</v>
+      </c>
+      <c r="U82">
+        <v>0.0912</v>
+      </c>
+      <c r="V82">
+        <v>0.265</v>
+      </c>
+      <c r="W82">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>1.575900881100301</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1014756152208956</v>
+      </c>
+      <c r="C83">
+        <v>1.245561335739845</v>
+      </c>
+      <c r="D83">
+        <v>13.66316133573985</v>
+      </c>
+      <c r="E83">
+        <v>10.7876</v>
+      </c>
+      <c r="F83">
+        <v>14.5476</v>
+      </c>
+      <c r="G83">
+        <v>2.13</v>
+      </c>
+      <c r="H83">
+        <v>14.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>3.125</v>
+      </c>
+      <c r="K83">
+        <v>1.06</v>
+      </c>
+      <c r="L83">
+        <v>2.065</v>
+      </c>
+      <c r="M83">
+        <v>1.32674112</v>
+      </c>
+      <c r="N83">
+        <v>0.7382588799999998</v>
+      </c>
+      <c r="O83">
+        <v>0.1956386032</v>
+      </c>
+      <c r="P83">
+        <v>0.5426202767999999</v>
+      </c>
+      <c r="Q83">
+        <v>1.6026202768</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.248314185373135</v>
+      </c>
+      <c r="T83">
+        <v>4.554656203763804</v>
+      </c>
+      <c r="U83">
+        <v>0.0912</v>
+      </c>
+      <c r="V83">
+        <v>0.265</v>
+      </c>
+      <c r="W83">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>1.556445314666964</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1016236124446362</v>
+      </c>
+      <c r="C84">
+        <v>1.047652391136156</v>
+      </c>
+      <c r="D84">
+        <v>13.64485239113616</v>
+      </c>
+      <c r="E84">
+        <v>10.9672</v>
+      </c>
+      <c r="F84">
+        <v>14.7272</v>
+      </c>
+      <c r="G84">
+        <v>2.13</v>
+      </c>
+      <c r="H84">
+        <v>14.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>3.125</v>
+      </c>
+      <c r="K84">
+        <v>1.06</v>
+      </c>
+      <c r="L84">
+        <v>2.065</v>
+      </c>
+      <c r="M84">
+        <v>1.34312064</v>
+      </c>
+      <c r="N84">
+        <v>0.7218793599999997</v>
+      </c>
+      <c r="O84">
+        <v>0.1912980303999999</v>
+      </c>
+      <c r="P84">
+        <v>0.5305813295999998</v>
+      </c>
+      <c r="Q84">
+        <v>1.5905813296</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2592076246924233</v>
+      </c>
+      <c r="T84">
+        <v>4.791470102009201</v>
+      </c>
+      <c r="U84">
+        <v>0.0912</v>
+      </c>
+      <c r="V84">
+        <v>0.265</v>
+      </c>
+      <c r="W84">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>1.537464274244196</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1017716096683767</v>
+      </c>
+      <c r="C85">
+        <v>0.8497924496652605</v>
+      </c>
+      <c r="D85">
+        <v>13.62659244966526</v>
+      </c>
+      <c r="E85">
+        <v>11.1468</v>
+      </c>
+      <c r="F85">
+        <v>14.9068</v>
+      </c>
+      <c r="G85">
+        <v>2.13</v>
+      </c>
+      <c r="H85">
+        <v>14.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>3.125</v>
+      </c>
+      <c r="K85">
+        <v>1.06</v>
+      </c>
+      <c r="L85">
+        <v>2.065</v>
+      </c>
+      <c r="M85">
+        <v>1.35950016</v>
+      </c>
+      <c r="N85">
+        <v>0.7054998399999997</v>
+      </c>
+      <c r="O85">
+        <v>0.1869574575999999</v>
+      </c>
+      <c r="P85">
+        <v>0.5185423823999997</v>
+      </c>
+      <c r="Q85">
+        <v>1.5785423824</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2713826451080983</v>
+      </c>
+      <c r="T85">
+        <v>5.056144458871703</v>
+      </c>
+      <c r="U85">
+        <v>0.0912</v>
+      </c>
+      <c r="V85">
+        <v>0.265</v>
+      </c>
+      <c r="W85">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>1.518940608289446</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1019196068921172</v>
+      </c>
+      <c r="C86">
+        <v>0.6519813148578013</v>
+      </c>
+      <c r="D86">
+        <v>13.6083813148578</v>
+      </c>
+      <c r="E86">
+        <v>11.3264</v>
+      </c>
+      <c r="F86">
+        <v>15.0864</v>
+      </c>
+      <c r="G86">
+        <v>2.13</v>
+      </c>
+      <c r="H86">
+        <v>14.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>3.125</v>
+      </c>
+      <c r="K86">
+        <v>1.06</v>
+      </c>
+      <c r="L86">
+        <v>2.065</v>
+      </c>
+      <c r="M86">
+        <v>1.37587968</v>
+      </c>
+      <c r="N86">
+        <v>0.68912032</v>
+      </c>
+      <c r="O86">
+        <v>0.1826168848</v>
+      </c>
+      <c r="P86">
+        <v>0.5065034352</v>
+      </c>
+      <c r="Q86">
+        <v>1.5665034352</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2850795430757327</v>
+      </c>
+      <c r="T86">
+        <v>5.353903110342014</v>
+      </c>
+      <c r="U86">
+        <v>0.0912</v>
+      </c>
+      <c r="V86">
+        <v>0.265</v>
+      </c>
+      <c r="W86">
+        <v>0.06703199999999999</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>1.500857982000287</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1492865916098647</v>
+      </c>
+      <c r="C87">
+        <v>-3.60453351030951</v>
+      </c>
+      <c r="D87">
+        <v>9.531466489690489</v>
+      </c>
+      <c r="E87">
+        <v>11.506</v>
+      </c>
+      <c r="F87">
+        <v>15.266</v>
+      </c>
+      <c r="G87">
+        <v>2.13</v>
+      </c>
+      <c r="H87">
+        <v>14.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>3.125</v>
+      </c>
+      <c r="K87">
+        <v>1.06</v>
+      </c>
+      <c r="L87">
+        <v>2.065</v>
+      </c>
+      <c r="M87">
+        <v>2.3906556</v>
+      </c>
+      <c r="N87">
+        <v>-0.3256556000000002</v>
+      </c>
+      <c r="O87">
+        <v>-0.08629873400000004</v>
+      </c>
+      <c r="P87">
+        <v>-0.2393568660000001</v>
+      </c>
+      <c r="Q87">
+        <v>0.820643134</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3109712640360691</v>
+      </c>
+      <c r="T87">
+        <v>5.916766609479763</v>
+      </c>
+      <c r="U87">
+        <v>0.1566</v>
+      </c>
+      <c r="V87">
+        <v>0.2289016452223398</v>
+      </c>
+      <c r="W87">
+        <v>0.1207540023581816</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.8637797932918484</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1504645916098648</v>
+      </c>
+      <c r="C88">
+        <v>-3.854624021369611</v>
+      </c>
+      <c r="D88">
+        <v>9.460975978630389</v>
+      </c>
+      <c r="E88">
+        <v>11.6856</v>
+      </c>
+      <c r="F88">
+        <v>15.4456</v>
+      </c>
+      <c r="G88">
+        <v>2.13</v>
+      </c>
+      <c r="H88">
+        <v>14.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>3.125</v>
+      </c>
+      <c r="K88">
+        <v>1.06</v>
+      </c>
+      <c r="L88">
+        <v>2.065</v>
+      </c>
+      <c r="M88">
+        <v>2.41878096</v>
+      </c>
+      <c r="N88">
+        <v>-0.3537809600000004</v>
+      </c>
+      <c r="O88">
+        <v>-0.0937519544000001</v>
+      </c>
+      <c r="P88">
+        <v>-0.2600290056000003</v>
+      </c>
+      <c r="Q88">
+        <v>0.7999709943999997</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.330412068610074</v>
+      </c>
+      <c r="T88">
+        <v>6.339392795871174</v>
+      </c>
+      <c r="U88">
+        <v>0.1566</v>
+      </c>
+      <c r="V88">
+        <v>0.2262399981848708</v>
+      </c>
+      <c r="W88">
+        <v>0.1211708162842493</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.8537358422070594</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1516425916098647</v>
+      </c>
+      <c r="C89">
+        <v>-4.103679553383438</v>
+      </c>
+      <c r="D89">
+        <v>9.391520446616564</v>
+      </c>
+      <c r="E89">
+        <v>11.8652</v>
+      </c>
+      <c r="F89">
+        <v>15.6252</v>
+      </c>
+      <c r="G89">
+        <v>2.13</v>
+      </c>
+      <c r="H89">
+        <v>14.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>3.125</v>
+      </c>
+      <c r="K89">
+        <v>1.06</v>
+      </c>
+      <c r="L89">
+        <v>2.065</v>
+      </c>
+      <c r="M89">
+        <v>2.446906320000001</v>
+      </c>
+      <c r="N89">
+        <v>-0.3819063200000006</v>
+      </c>
+      <c r="O89">
+        <v>-0.1012051748000002</v>
+      </c>
+      <c r="P89">
+        <v>-0.2807011452000004</v>
+      </c>
+      <c r="Q89">
+        <v>0.7792988547999996</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3528437661954643</v>
+      </c>
+      <c r="T89">
+        <v>6.827038395553572</v>
+      </c>
+      <c r="U89">
+        <v>0.1566</v>
+      </c>
+      <c r="V89">
+        <v>0.2236395384356193</v>
+      </c>
+      <c r="W89">
+        <v>0.121578048280982</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.8439227865495069</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1528205916098647</v>
+      </c>
+      <c r="C90">
+        <v>-4.351722734398898</v>
+      </c>
+      <c r="D90">
+        <v>9.323077265601103</v>
+      </c>
+      <c r="E90">
+        <v>12.0448</v>
+      </c>
+      <c r="F90">
+        <v>15.8048</v>
+      </c>
+      <c r="G90">
+        <v>2.13</v>
+      </c>
+      <c r="H90">
+        <v>14.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>3.125</v>
+      </c>
+      <c r="K90">
+        <v>1.06</v>
+      </c>
+      <c r="L90">
+        <v>2.065</v>
+      </c>
+      <c r="M90">
+        <v>2.47503168</v>
+      </c>
+      <c r="N90">
+        <v>-0.4100316800000003</v>
+      </c>
+      <c r="O90">
+        <v>-0.1086583952000001</v>
+      </c>
+      <c r="P90">
+        <v>-0.3013732848000003</v>
+      </c>
+      <c r="Q90">
+        <v>0.7586267151999998</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3790140800450864</v>
+      </c>
+      <c r="T90">
+        <v>7.395958261849704</v>
+      </c>
+      <c r="U90">
+        <v>0.1566</v>
+      </c>
+      <c r="V90">
+        <v>0.2210981800443055</v>
+      </c>
+      <c r="W90">
+        <v>0.1219760250050618</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.8343327548841717</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1539985916098647</v>
+      </c>
+      <c r="C91">
+        <v>-4.598775537604904</v>
+      </c>
+      <c r="D91">
+        <v>9.255624462395096</v>
+      </c>
+      <c r="E91">
+        <v>12.2244</v>
+      </c>
+      <c r="F91">
+        <v>15.9844</v>
+      </c>
+      <c r="G91">
+        <v>2.13</v>
+      </c>
+      <c r="H91">
+        <v>14.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>3.125</v>
+      </c>
+      <c r="K91">
+        <v>1.06</v>
+      </c>
+      <c r="L91">
+        <v>2.065</v>
+      </c>
+      <c r="M91">
+        <v>2.50315704</v>
+      </c>
+      <c r="N91">
+        <v>-0.4381570400000006</v>
+      </c>
+      <c r="O91">
+        <v>-0.1161116156000001</v>
+      </c>
+      <c r="P91">
+        <v>-0.3220454244000004</v>
+      </c>
+      <c r="Q91">
+        <v>0.7379545755999997</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4099426327764579</v>
+      </c>
+      <c r="T91">
+        <v>8.068318103836042</v>
+      </c>
+      <c r="U91">
+        <v>0.1566</v>
+      </c>
+      <c r="V91">
+        <v>0.2186139308303245</v>
+      </c>
+      <c r="W91">
+        <v>0.1223650584319712</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.8249582295483944</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1551765916098647</v>
+      </c>
+      <c r="C92">
+        <v>-4.844859304850857</v>
+      </c>
+      <c r="D92">
+        <v>9.189140695149145</v>
+      </c>
+      <c r="E92">
+        <v>12.404</v>
+      </c>
+      <c r="F92">
+        <v>16.164</v>
+      </c>
+      <c r="G92">
+        <v>2.13</v>
+      </c>
+      <c r="H92">
+        <v>14.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>3.125</v>
+      </c>
+      <c r="K92">
+        <v>1.06</v>
+      </c>
+      <c r="L92">
+        <v>2.065</v>
+      </c>
+      <c r="M92">
+        <v>2.531282400000001</v>
+      </c>
+      <c r="N92">
+        <v>-0.4662824000000008</v>
+      </c>
+      <c r="O92">
+        <v>-0.1235648360000002</v>
+      </c>
+      <c r="P92">
+        <v>-0.3427175640000005</v>
+      </c>
+      <c r="Q92">
+        <v>0.7172824359999995</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4470568960541036</v>
+      </c>
+      <c r="T92">
+        <v>8.875149914219644</v>
+      </c>
+      <c r="U92">
+        <v>0.1566</v>
+      </c>
+      <c r="V92">
+        <v>0.216184887154432</v>
+      </c>
+      <c r="W92">
+        <v>0.122745446671616</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.8157920269978567</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1563545916098647</v>
+      </c>
+      <c r="C93">
+        <v>-5.089994769159674</v>
+      </c>
+      <c r="D93">
+        <v>9.123605230840329</v>
+      </c>
+      <c r="E93">
+        <v>12.5836</v>
+      </c>
+      <c r="F93">
+        <v>16.3436</v>
+      </c>
+      <c r="G93">
+        <v>2.13</v>
+      </c>
+      <c r="H93">
+        <v>14.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>3.125</v>
+      </c>
+      <c r="K93">
+        <v>1.06</v>
+      </c>
+      <c r="L93">
+        <v>2.065</v>
+      </c>
+      <c r="M93">
+        <v>2.55940776</v>
+      </c>
+      <c r="N93">
+        <v>-0.4944077600000005</v>
+      </c>
+      <c r="O93">
+        <v>-0.1310180564000001</v>
+      </c>
+      <c r="P93">
+        <v>-0.3633897036000004</v>
+      </c>
+      <c r="Q93">
+        <v>0.6966102963999996</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4924187733934486</v>
+      </c>
+      <c r="T93">
+        <v>9.861277682466275</v>
+      </c>
+      <c r="U93">
+        <v>0.1566</v>
+      </c>
+      <c r="V93">
+        <v>0.2138092290538339</v>
+      </c>
+      <c r="W93">
+        <v>0.1231174747301696</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.8068272794484297</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2080221292329903</v>
+      </c>
+      <c r="C94">
+        <v>-7.443497726257689</v>
+      </c>
+      <c r="D94">
+        <v>6.949702273742314</v>
+      </c>
+      <c r="E94">
+        <v>12.7632</v>
+      </c>
+      <c r="F94">
+        <v>16.5232</v>
+      </c>
+      <c r="G94">
+        <v>2.13</v>
+      </c>
+      <c r="H94">
+        <v>14.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>3.125</v>
+      </c>
+      <c r="K94">
+        <v>1.06</v>
+      </c>
+      <c r="L94">
+        <v>2.065</v>
+      </c>
+      <c r="M94">
+        <v>3.450044160000001</v>
+      </c>
+      <c r="N94">
+        <v>-1.385044160000001</v>
+      </c>
+      <c r="O94">
+        <v>-0.3670367024000002</v>
+      </c>
+      <c r="P94">
+        <v>-1.018007457600001</v>
+      </c>
+      <c r="Q94">
+        <v>0.04199254239999939</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5799403403566992</v>
+      </c>
+      <c r="T94">
+        <v>11.76392044253694</v>
+      </c>
+      <c r="U94">
+        <v>0.2088</v>
+      </c>
+      <c r="V94">
+        <v>0.1586139117709148</v>
+      </c>
+      <c r="W94">
+        <v>0.175681415222233</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.598543063286471</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2097221292329903</v>
+      </c>
+      <c r="C95">
+        <v>-7.677158159387821</v>
+      </c>
+      <c r="D95">
+        <v>6.895641840612183</v>
+      </c>
+      <c r="E95">
+        <v>12.9428</v>
+      </c>
+      <c r="F95">
+        <v>16.7028</v>
+      </c>
+      <c r="G95">
+        <v>2.13</v>
+      </c>
+      <c r="H95">
+        <v>14.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>3.125</v>
+      </c>
+      <c r="K95">
+        <v>1.06</v>
+      </c>
+      <c r="L95">
+        <v>2.065</v>
+      </c>
+      <c r="M95">
+        <v>3.487544640000001</v>
+      </c>
+      <c r="N95">
+        <v>-1.422544640000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.3769743296000002</v>
+      </c>
+      <c r="P95">
+        <v>-1.0455703104</v>
+      </c>
+      <c r="Q95">
+        <v>0.01442968959999957</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6572461032647992</v>
+      </c>
+      <c r="T95">
+        <v>13.4444805057565</v>
+      </c>
+      <c r="U95">
+        <v>0.2088</v>
+      </c>
+      <c r="V95">
+        <v>0.1569083858378942</v>
+      </c>
+      <c r="W95">
+        <v>0.1760375290370477</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.592107116369412</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2114221292329903</v>
+      </c>
+      <c r="C96">
+        <v>-7.909984032424319</v>
+      </c>
+      <c r="D96">
+        <v>6.842415967575682</v>
+      </c>
+      <c r="E96">
+        <v>13.1224</v>
+      </c>
+      <c r="F96">
+        <v>16.8824</v>
+      </c>
+      <c r="G96">
+        <v>2.13</v>
+      </c>
+      <c r="H96">
+        <v>14.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>3.125</v>
+      </c>
+      <c r="K96">
+        <v>1.06</v>
+      </c>
+      <c r="L96">
+        <v>2.065</v>
+      </c>
+      <c r="M96">
+        <v>3.52504512</v>
+      </c>
+      <c r="N96">
+        <v>-1.46004512</v>
+      </c>
+      <c r="O96">
+        <v>-0.3869119568000001</v>
+      </c>
+      <c r="P96">
+        <v>-1.0731331632</v>
+      </c>
+      <c r="Q96">
+        <v>-0.01313316320000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7603204538089328</v>
+      </c>
+      <c r="T96">
+        <v>15.68522725671593</v>
+      </c>
+      <c r="U96">
+        <v>0.2088</v>
+      </c>
+      <c r="V96">
+        <v>0.1552391476906826</v>
+      </c>
+      <c r="W96">
+        <v>0.1763860659621855</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5858081044931418</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2131221292329903</v>
+      </c>
+      <c r="C97">
+        <v>-8.141994522674086</v>
+      </c>
+      <c r="D97">
+        <v>6.790005477325916</v>
+      </c>
+      <c r="E97">
+        <v>13.302</v>
+      </c>
+      <c r="F97">
+        <v>17.062</v>
+      </c>
+      <c r="G97">
+        <v>2.13</v>
+      </c>
+      <c r="H97">
+        <v>14.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>3.125</v>
+      </c>
+      <c r="K97">
+        <v>1.06</v>
+      </c>
+      <c r="L97">
+        <v>2.065</v>
+      </c>
+      <c r="M97">
+        <v>3.5625456</v>
+      </c>
+      <c r="N97">
+        <v>-1.4975456</v>
+      </c>
+      <c r="O97">
+        <v>-0.3968495840000001</v>
+      </c>
+      <c r="P97">
+        <v>-1.100696016</v>
+      </c>
+      <c r="Q97">
+        <v>-0.04069601600000028</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9046245445707193</v>
+      </c>
+      <c r="T97">
+        <v>18.82227270805912</v>
+      </c>
+      <c r="U97">
+        <v>0.2088</v>
+      </c>
+      <c r="V97">
+        <v>0.1536050513992017</v>
+      </c>
+      <c r="W97">
+        <v>0.1767272652678467</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.579641703393214</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2148221292329903</v>
+      </c>
+      <c r="C98">
+        <v>-8.373208224344758</v>
+      </c>
+      <c r="D98">
+        <v>6.738391775655244</v>
+      </c>
+      <c r="E98">
+        <v>13.4816</v>
+      </c>
+      <c r="F98">
+        <v>17.2416</v>
+      </c>
+      <c r="G98">
+        <v>2.13</v>
+      </c>
+      <c r="H98">
+        <v>14.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>3.125</v>
+      </c>
+      <c r="K98">
+        <v>1.06</v>
+      </c>
+      <c r="L98">
+        <v>2.065</v>
+      </c>
+      <c r="M98">
+        <v>3.600046080000001</v>
+      </c>
+      <c r="N98">
+        <v>-1.535046080000001</v>
+      </c>
+      <c r="O98">
+        <v>-0.4067872112000002</v>
+      </c>
+      <c r="P98">
+        <v>-1.128258868800001</v>
+      </c>
+      <c r="Q98">
+        <v>-0.06825886880000054</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.121080680713397</v>
+      </c>
+      <c r="T98">
+        <v>23.52784088507385</v>
+      </c>
+      <c r="U98">
+        <v>0.2088</v>
+      </c>
+      <c r="V98">
+        <v>0.15200499878046</v>
+      </c>
+      <c r="W98">
+        <v>0.17706135625464</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.573603768982868</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2165221292329903</v>
+      </c>
+      <c r="C99">
+        <v>-8.603643170539431</v>
+      </c>
+      <c r="D99">
+        <v>6.687556829460567</v>
+      </c>
+      <c r="E99">
+        <v>13.6612</v>
+      </c>
+      <c r="F99">
+        <v>17.4212</v>
+      </c>
+      <c r="G99">
+        <v>2.13</v>
+      </c>
+      <c r="H99">
+        <v>14.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>3.125</v>
+      </c>
+      <c r="K99">
+        <v>1.06</v>
+      </c>
+      <c r="L99">
+        <v>2.065</v>
+      </c>
+      <c r="M99">
+        <v>3.63754656</v>
+      </c>
+      <c r="N99">
+        <v>-1.57254656</v>
+      </c>
+      <c r="O99">
+        <v>-0.4167248384000001</v>
+      </c>
+      <c r="P99">
+        <v>-1.1558217216</v>
+      </c>
+      <c r="Q99">
+        <v>-0.09582172160000013</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.481840907617863</v>
+      </c>
+      <c r="T99">
+        <v>31.3704545134318</v>
+      </c>
+      <c r="U99">
+        <v>0.2088</v>
+      </c>
+      <c r="V99">
+        <v>0.1504379369373625</v>
+      </c>
+      <c r="W99">
+        <v>0.1773885587674787</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.567690328065519</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2182221292329903</v>
+      </c>
+      <c r="C100">
+        <v>-8.833316854263291</v>
+      </c>
+      <c r="D100">
+        <v>6.637483145736708</v>
+      </c>
+      <c r="E100">
+        <v>13.8408</v>
+      </c>
+      <c r="F100">
+        <v>17.6008</v>
+      </c>
+      <c r="G100">
+        <v>2.13</v>
+      </c>
+      <c r="H100">
+        <v>14.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>3.125</v>
+      </c>
+      <c r="K100">
+        <v>1.06</v>
+      </c>
+      <c r="L100">
+        <v>2.065</v>
+      </c>
+      <c r="M100">
+        <v>3.67504704</v>
+      </c>
+      <c r="N100">
+        <v>-1.61004704</v>
+      </c>
+      <c r="O100">
+        <v>-0.4266624656</v>
+      </c>
+      <c r="P100">
+        <v>-1.1833845744</v>
+      </c>
+      <c r="Q100">
+        <v>-0.1233845743999999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.203361361426794</v>
+      </c>
+      <c r="T100">
+        <v>47.05568177014769</v>
+      </c>
+      <c r="U100">
+        <v>0.2088</v>
+      </c>
+      <c r="V100">
+        <v>0.1489028559482058</v>
+      </c>
+      <c r="W100">
+        <v>0.1777090836780147</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.5618975696158708</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2199221292329903</v>
+      </c>
+      <c r="C101">
+        <v>-9.062246248493455</v>
+      </c>
+      <c r="D101">
+        <v>6.588153751506544</v>
+      </c>
+      <c r="E101">
+        <v>14.0204</v>
+      </c>
+      <c r="F101">
+        <v>17.7804</v>
+      </c>
+      <c r="G101">
+        <v>2.13</v>
+      </c>
+      <c r="H101">
+        <v>14.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>3.125</v>
+      </c>
+      <c r="K101">
+        <v>1.06</v>
+      </c>
+      <c r="L101">
+        <v>2.065</v>
+      </c>
+      <c r="M101">
+        <v>3.71254752</v>
+      </c>
+      <c r="N101">
+        <v>-1.64754752</v>
+      </c>
+      <c r="O101">
+        <v>-0.4366000928000001</v>
+      </c>
+      <c r="P101">
+        <v>-1.2109474272</v>
+      </c>
+      <c r="Q101">
+        <v>-0.1509474272000002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.367922722853588</v>
+      </c>
+      <c r="T101">
+        <v>94.11136354029539</v>
+      </c>
+      <c r="U101">
+        <v>0.2088</v>
+      </c>
+      <c r="V101">
+        <v>0.1473987866962037</v>
+      </c>
+      <c r="W101">
+        <v>0.1780231333378327</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.5562218365894478</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
